--- a/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3616600</v>
+      </c>
+      <c r="E8" s="3">
         <v>3310200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3095700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3041100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3451600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3156000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2942600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2899600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3222100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2688900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2280500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1763600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1566600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1212200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>882000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>714900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>777200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>610100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>436200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>351900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>283200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>204900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>183800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>155000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>124600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>94100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>101500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>93900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>88500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2091800</v>
+      </c>
+      <c r="E9" s="3">
         <v>1868900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1644800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1624400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1754300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1928200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1852400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1729500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1911400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1680200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1349700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1118200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1032800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>804600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>681200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>508100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>512400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>407000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>338700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>312400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>291200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>199300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>175200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>146500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>101100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>83300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>75700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>66800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>63200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1524800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1441300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1450900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1416700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1697300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1227800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1090200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1170100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1310700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1008700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>930800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>645400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>533800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>407600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>200800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>206800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>264800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>203100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>97500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>39500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-8000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>23500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>10800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>25800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>27100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>25300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1110,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>279800</v>
+      </c>
+      <c r="E12" s="3">
         <v>280500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>283300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>320500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>244200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>421000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>370900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>340400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>286600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>231400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>172600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>141100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>109500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>104300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>75300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>63900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>48800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>43600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>35100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>28500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>26600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>17300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,31 +1298,34 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-38600</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>117900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-22000</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>177300</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>11</v>
@@ -1323,8 +1342,8 @@
       <c r="O14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1403,8 +1425,8 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>11</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>11</v>
@@ -1421,14 +1443,14 @@
       <c r="Q15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S15" s="3">
         <v>11000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>10100</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>11</v>
@@ -1454,20 +1476,23 @@
       <c r="AB15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD15" s="3">
         <v>2100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2000</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3634600</v>
+      </c>
+      <c r="E17" s="3">
         <v>3437900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2811800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2915900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2909000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3651600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3779300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3397600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3664200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3147400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2614600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2112100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1923900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1517600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1254800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>982600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1007300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>797600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>670700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>591100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>608200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>451100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>403300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>353100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>315700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>254800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>184000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>162000</v>
       </c>
-      <c r="AE17" s="3" t="s">
+      <c r="AF17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-127700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>283900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>125200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>542600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-495600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-836700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-498000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-442100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-458500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-334100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-348500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-357300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-305400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-372800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-267700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-230100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-187500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-234500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-239200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-325000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-246200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-219500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-198100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-191100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-160700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-82500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-68100</v>
       </c>
-      <c r="AE18" s="3" t="s">
+      <c r="AF18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-52900</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E20" s="3">
         <v>56000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>117900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>32900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-153900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-21400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-18700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>24200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-89600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>51000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>35900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>20600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-19100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-432700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>62900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>40800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-27800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-53200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>34300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-200</v>
       </c>
-      <c r="AE20" s="3" t="s">
+      <c r="AF20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-76500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>393600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>278300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>384000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-476300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-844500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-402800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-258200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-420100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-331200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-287800</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R21" s="3">
         <v>-318400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-193600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-193500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-108900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-250100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-646400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-287600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-171100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-244000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-193200</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-73900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-59400</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E22" s="3">
         <v>10200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>10400</v>
       </c>
       <c r="F22" s="3">
         <v>10400</v>
       </c>
       <c r="G22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="H22" s="3">
         <v>10800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>52300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>37000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>22700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>26900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>34900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>45400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>43300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>17200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>10800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>9900</v>
       </c>
       <c r="X22" s="3">
         <v>9900</v>
       </c>
       <c r="Y22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="Z22" s="3">
         <v>3000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2300</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-81900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>391400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>147700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>377800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-504800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-869500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-504100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-513100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-471400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-359100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-371700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-481800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-379800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-365200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-256500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-245200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-177700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-263700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-682000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-272000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-215300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-250300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-216300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-253400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-134900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-89700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-70500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-56800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E24" s="3">
         <v>61700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>62200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>61900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-43500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>65300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>81800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>105600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>101000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>75200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>51000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>44200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>46400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>27800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>36000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>27400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>8700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-101800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-143500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>329200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>85800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>421300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-570100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-934200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-585900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-618700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-572400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-434300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-422700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-526000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-426200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-393000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-279700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-281200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-205000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-279000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-689200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-275000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-217300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-250100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-215600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-262200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-132800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-91900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-72400</v>
       </c>
-      <c r="AE26" s="3" t="s">
+      <c r="AF26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-60300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-109700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-149200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>321600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>88100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>426800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-565300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-933100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-579800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-617600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-573000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-433400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-422700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-523600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-420000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-393000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-281500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-283800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-207600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-281100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-690400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-276600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-218300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-250700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-215600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-262700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-132700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-92100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-73100</v>
       </c>
-      <c r="AE27" s="3" t="s">
+      <c r="AF27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-56000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-117900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-32900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>153900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>21400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>18700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-24200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>89600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>28900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-51000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-35900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-20600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>19100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>432700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-62900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-40800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>27800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>9600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>53200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-34300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>200</v>
       </c>
-      <c r="AE32" s="3" t="s">
+      <c r="AF32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-109700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-149200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>321600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>88100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>426800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-565300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-933100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-579800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-617600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-573000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-433400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-422700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-523600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-420000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-393000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-281500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-283800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-207600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-281100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-690400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-276600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-218300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-250700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-215600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-262700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-132700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-92100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-73100</v>
       </c>
-      <c r="AE33" s="3" t="s">
+      <c r="AF33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-109700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-149200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>321600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>88100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>426800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-565300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-933100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-579800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-617600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-573000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-433400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-422700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-523600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-420000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-393000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-281500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-283800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-207600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-281100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-690400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-276600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-218300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-250700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-215600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-262700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-132700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-92100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-73100</v>
       </c>
-      <c r="AE35" s="3" t="s">
+      <c r="AF35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,166 +3437,170 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2811100</v>
+      </c>
+      <c r="E41" s="3">
         <v>3219900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3524400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6082700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6029900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6253400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6493200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7683700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9247800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11126200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4645400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5752600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6166900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3509000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3432800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2599700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3119000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2297200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2308100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2362500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1002800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1209200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1477100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1172400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1347400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>581500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>651100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>456800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>170100</v>
       </c>
-      <c r="AF41" s="3" t="s">
+      <c r="AG41" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2547600</v>
+      </c>
+      <c r="E42" s="3">
         <v>2762700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2174900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>506400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>864300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1042300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1287500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1116900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>911300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>706000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>962100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>309700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>126100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>42300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>14700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>30500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>102300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>8900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>700</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
@@ -3519,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
         <v>18000</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AC42" s="3" t="s">
         <v>11</v>
@@ -3530,658 +3619,682 @@
       <c r="AD42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="3" t="s">
+      <c r="AE42" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3017600</v>
+      </c>
+      <c r="E43" s="3">
         <v>2313000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2198800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2246600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2336000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2386500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2295000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2124600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1905400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1433700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1159100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>795400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>668400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>295900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>254600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>163600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>191800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>140500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>152700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>151500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>103000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>66500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>61000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>73100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>64100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>59200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>47900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>43200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>37800</v>
       </c>
-      <c r="AF43" s="3" t="s">
+      <c r="AG43" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E44" s="3">
         <v>116300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>98500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>107300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>109700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>122400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>127200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>139700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>117500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>128700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>99500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>92700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>64200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>61700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>61200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>34200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>26900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>21400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>22500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>25900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>37700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>19600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>16900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>13400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>9800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>7300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3900</v>
       </c>
-      <c r="AF44" s="3" t="s">
+      <c r="AG44" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3272200</v>
+      </c>
+      <c r="E45" s="3">
         <v>3562000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3479200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3497300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3348200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2773300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2769200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2765100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2953500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2609100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2530900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2075600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1913400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1654200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1487700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1222600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>970100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>849300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>757500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>652000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>566500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>513100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>424200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>383400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>281500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>218800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>163600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>122800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>98100</v>
       </c>
-      <c r="AF45" s="3" t="s">
+      <c r="AG45" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11773900</v>
+      </c>
+      <c r="E46" s="3">
         <v>11973900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11475800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12440300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12688000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12577900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12972100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13829900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15135400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16003700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9397100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9025900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8939000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5563100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5251000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4050600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4410100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3317800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3249700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3192500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1710700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1808500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1979300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1642300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1720700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>866800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>868200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>628600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>309900</v>
       </c>
-      <c r="AF46" s="3" t="s">
+      <c r="AG46" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4283100</v>
+      </c>
+      <c r="E47" s="3">
         <v>3182600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3202100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1805500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1275300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1372000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1383900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1455900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1081800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>370600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>331900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>353500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>307600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>219100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>195200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>143200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>113800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>99100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>100400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>107100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>111000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>118200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>71000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>58500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>28200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>27100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>45100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>45400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45100</v>
       </c>
-      <c r="AF47" s="3" t="s">
+      <c r="AG47" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2223700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2243800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2308400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2372400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2345700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2457200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2214700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2101500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1679600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1353300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>830200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>628600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>621000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>573400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>523500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>486900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>501600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>463100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>425900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>406300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>192400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>147400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>121900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>93900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>74300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>47900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>34100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>32400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>31100</v>
       </c>
-      <c r="AF48" s="3" t="s">
+      <c r="AG48" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E49" s="3">
         <v>173400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>176300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>182300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>295200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>482100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>462300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>624000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>592100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>525400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>518500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>509300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>256100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>244000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>260500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>263300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>46000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>45900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>43800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>44900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>43800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>56600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>60500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>64600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>68300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>73000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>24300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>27200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>30000</v>
       </c>
-      <c r="AF49" s="3" t="s">
+      <c r="AG49" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>438900</v>
+      </c>
+      <c r="E52" s="3">
         <v>451400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>489700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>443400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>398600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>393200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>434700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>323400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>267000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>295700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>445400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>405300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>332000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>360900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>374100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>288900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>152700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>156000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>199200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>176100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>134700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>121800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>122600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>111100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>96700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>106400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>92500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>78900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>69700</v>
       </c>
-      <c r="AF52" s="3" t="s">
+      <c r="AG52" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18883200</v>
+      </c>
+      <c r="E54" s="3">
         <v>18025100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17652300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17243900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17002800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17282300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17467700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18334600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18756000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18548700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11523000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10922600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10455700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6960600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6604300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5232800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5224200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4081900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4019100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3927000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2192700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2252400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2355400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1970500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1988300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1121200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1064200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>812400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>485800</v>
       </c>
-      <c r="AF54" s="3" t="s">
+      <c r="AG54" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,129 +4837,133 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>342500</v>
+      </c>
+      <c r="E57" s="3">
         <v>267900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>219000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>212300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>258600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>289800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>239000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>287100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>213600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>232700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>179600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>152900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>121600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>118400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>96700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>51000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>69400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>48100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>32400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>38100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>37200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>25200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>33900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6000</v>
       </c>
-      <c r="AF57" s="3" t="s">
+      <c r="AG57" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2004700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1489000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1452600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1544400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1436000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>80200</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>100000</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>11</v>
@@ -4838,8 +4971,8 @@
       <c r="N58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4848,34 +4981,34 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>2400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>30700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>24000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>25800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>900</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-      <c r="Z58" s="3" t="s">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>2000</v>
       </c>
       <c r="AB58" s="3">
         <v>2000</v>
@@ -4887,381 +5020,396 @@
         <v>2000</v>
       </c>
       <c r="AE58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF58" s="3">
         <v>1900</v>
       </c>
-      <c r="AF58" s="3" t="s">
+      <c r="AG58" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5821700</v>
+      </c>
+      <c r="E59" s="3">
         <v>5274000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4904100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4903500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5241000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6681300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6500800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6567000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6862900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6188300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5704000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4924700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4514400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3654100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2890200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2375300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2262300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1979600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1663600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1371000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1148500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>921400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>744000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>738400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>627000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>438500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>323700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>276700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>255900</v>
       </c>
-      <c r="AF59" s="3" t="s">
+      <c r="AG59" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8168900</v>
+      </c>
+      <c r="E60" s="3">
         <v>7030800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6575700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6660200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6935700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7051400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6739800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6854100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7176400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6421000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5883600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5077600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4636100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3772500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2986900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2428600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2362400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2051700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1721800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1410100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1186500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>946500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>777900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>752300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>637700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>449800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>333800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>288100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>263800</v>
       </c>
-      <c r="AF60" s="3" t="s">
+      <c r="AG60" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3069100</v>
+      </c>
+      <c r="E61" s="3">
         <v>3439700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3391700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3340200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3338800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4148000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4177300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4175400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3475700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3503500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1282500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1757600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1840400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1920900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2109200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1374800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1356700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>446600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>439600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>582700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1062800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1116400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1145800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>745700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>727000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>674400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>624800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>355000</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>947600</v>
+      </c>
+      <c r="E62" s="3">
         <v>976500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1064600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1051800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>917500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1126800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1115800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1013800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>679500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>813800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>758000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>647000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>559000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>494400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>615700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>462400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>332500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>324100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>418800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>400200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>182800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>161300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>200200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>177900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>148500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>208100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>179600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>157100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>142600</v>
       </c>
-      <c r="AF62" s="3" t="s">
+      <c r="AG62" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12289400</v>
+      </c>
+      <c r="E66" s="3">
         <v>11557800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11140800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11150600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11287100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12385100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12094500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12073400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11357300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10761500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7962900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7518900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7072800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6219300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5750500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4312200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4061700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2829400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2585700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2397500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2435800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2227300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2126800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1681400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1519300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1340700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1138200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>800200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>406400</v>
       </c>
-      <c r="AF66" s="3" t="s">
+      <c r="AG66" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5924,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
-        <v>205100</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="3">
         <v>205100</v>
@@ -5936,10 +6103,13 @@
         <v>205100</v>
       </c>
       <c r="AF70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+        <v>205100</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8582300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8472600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8323400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8645000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8733100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-9159800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8594600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7661400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7195400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6577700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6004700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5571300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5148600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4625000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4205000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3812100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3530500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3246800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3039200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2758100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2067700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1791100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1572800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1322100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1106500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-843800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-670100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-578000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-505000</v>
       </c>
-      <c r="AF72" s="3" t="s">
+      <c r="AG72" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6593800</v>
+      </c>
+      <c r="E76" s="3">
         <v>6467300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6511500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6093300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5715700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4897200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5373200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6261200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7398700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7787300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3560200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3403700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3382900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>741200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>853800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>920600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1162400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1252500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1433400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1529500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-243100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>25100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>228600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>289100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>469000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-424600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-279000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-192800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-125700</v>
       </c>
-      <c r="AF76" s="3" t="s">
+      <c r="AG76" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-109700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-149200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>321600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>88100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>426800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-565300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-933100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-579800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-617600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-573000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-433400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-422700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-523600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-420000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-393000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-281500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-283800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-207600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-281100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-690400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-276600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-218300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-250700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-215600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-262700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-132700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-92100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-73100</v>
       </c>
-      <c r="AE81" s="3" t="s">
+      <c r="AF81" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6846,20 +7044,20 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>11</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S83" s="3">
         <v>38200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>34600</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>11</v>
@@ -6873,32 +7071,35 @@
       <c r="X83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>11</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD83" s="3">
         <v>9000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8800</v>
-      </c>
-      <c r="AE83" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>278800</v>
+      </c>
+      <c r="E89" s="3">
         <v>599800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>595500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>605500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>319700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-166300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-485500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-723700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-304800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>62700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>132400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>318300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>185400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>296000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>298100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-223700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-27800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>380800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-265300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-17800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-324400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>112300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-188800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-94400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-38200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-89800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-65400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-65800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-42100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-36500</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7492,7 +7712,7 @@
         <v>-807200</v>
       </c>
       <c r="E91" s="3">
-        <v>-306300</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -7524,20 +7744,20 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>11</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S91" s="3">
         <v>-50100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-42400</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>11</v>
@@ -7551,32 +7771,35 @@
       <c r="X91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>11</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7400</v>
-      </c>
-      <c r="AE91" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1048600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-888300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3193900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-673800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>51500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-402100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-947500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1130700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1775500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-341900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1145500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-504300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-667400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>91300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-163700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-147100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-143700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-157700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>29400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-91300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-157100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-40000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-51100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-50100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>12900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-13400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>183400</v>
+      </c>
+      <c r="E100" s="3">
         <v>124500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>59200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-513700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>474000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>297600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>142400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>386000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6835200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>138800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>41600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2198600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>747700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>811600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-24800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1045000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>989800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-983100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1527900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-149800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>151700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>545300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>927400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>69500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>270000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>357000</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-54200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-71600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>49500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>109100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-124900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-119700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-33000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>14500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-46300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>59000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>13000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>60500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-51800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>23200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>12900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-12900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-16800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>15300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-17300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-518000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-218100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2671100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>40500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-219200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1255100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1687800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6523100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-859700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-190800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2068300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>855400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1006400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-447300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>896700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1225800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1231900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1420700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-648000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>273600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>299300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-110600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>842800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-69600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>194300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>286700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-31900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-18000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3734300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3616600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3310200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3095700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3041100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3451600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3156000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2942600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2899600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3222100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2688900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2280500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1763600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1566600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1212200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>882000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>714900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>777200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>610100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>436200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>351900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>283200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>204900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>183800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>155000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>124600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>94100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>101500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>93900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>88500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2180600</v>
+      </c>
+      <c r="E9" s="3">
         <v>2091800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1868900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1644800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1624400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1754300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1928200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1852400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1729500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1911400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1680200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1349700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1118200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1032800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>804600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>681200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>508100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>512400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>407000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>338700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>312400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>291200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>199300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>175200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>146500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>101100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>83300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>75700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>66800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>63200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1553700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1524800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1441300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1450900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1416700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1697300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1227800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1090200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1170100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1310700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1008700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>930800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>645400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>533800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>407600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>200800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>206800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>264800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>203100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>97500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>39500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>10800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>25800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>27100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>25300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>304400</v>
+      </c>
+      <c r="E12" s="3">
         <v>279800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>280500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>283300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>320500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>244200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>421000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>370900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>340400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>286600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>231400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>172600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>141100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>109500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>104300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>75300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>63900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>48800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>43600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>35100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>28500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>26600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>17300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>5800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,34 +1318,37 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-38600</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>117900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-22000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>177300</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>11</v>
@@ -1345,8 +1365,8 @@
       <c r="P14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1428,8 +1451,8 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>11</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>11</v>
@@ -1446,14 +1469,14 @@
       <c r="R15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T15" s="3">
         <v>11000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>10100</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>11</v>
@@ -1479,20 +1502,23 @@
       <c r="AC15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE15" s="3">
         <v>2100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2000</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3636100</v>
+      </c>
+      <c r="E17" s="3">
         <v>3634600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3437900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2811800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2915900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2909000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3651600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3779300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3397600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3664200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3147400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2614600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2112100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1923900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1517600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1254800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>982600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1007300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>797600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>670700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>591100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>608200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>451100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>403300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>353100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>315700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>254800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>184000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>162000</v>
       </c>
-      <c r="AF17" s="3" t="s">
+      <c r="AG17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-127700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>283900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>125200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>542600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-495600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-836700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-498000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-442100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-458500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-334100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-348500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-357300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-305400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-372800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-267700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-230100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-187500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-234500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-239200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-325000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-246200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-219500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-198100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-191100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-160700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-82500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-68100</v>
       </c>
-      <c r="AF18" s="3" t="s">
+      <c r="AG18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-52900</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E20" s="3">
         <v>3300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>56000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>117900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>32900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-153900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-21400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-18700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>24200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-89600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-28900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>51000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>35900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>20600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-19100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-432700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>62900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>40800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-27800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-53200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>34300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3" t="s">
+      <c r="AG20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>165500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-76500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>393600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>278300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>384000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-476300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-844500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-402800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-258200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-420100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-331200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-287800</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S21" s="3">
         <v>-318400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-193600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-193500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-108900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-250100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-646400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-287600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-171100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-244000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-193200</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-73900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-59400</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E22" s="3">
         <v>10100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>10400</v>
       </c>
       <c r="G22" s="3">
         <v>10400</v>
       </c>
       <c r="H22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I22" s="3">
         <v>10800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>52300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>37000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>22700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>26900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>34900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>45400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>43300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>24600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>17200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>10100</v>
-      </c>
-      <c r="X22" s="3">
-        <v>9900</v>
       </c>
       <c r="Y22" s="3">
         <v>9900</v>
       </c>
       <c r="Z22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AA22" s="3">
         <v>3000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2300</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-81900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>391400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>147700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>377800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-504800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-869500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-504100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-513100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-471400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-359100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-371700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-481800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-379800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-365200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-256500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-245200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-177700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-263700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-682000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-272000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-215300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-250300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-216300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-253400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-134900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-89700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-70500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-68000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-56800</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E24" s="3">
         <v>76900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>61700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>62200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>61900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-43500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>65300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>64800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>81800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>105600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>101000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>75200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>51000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>44200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>46400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>27800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>36000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>27400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>15300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>8700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-101800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-143500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>329200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>85800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>421300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-570100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-934200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-585900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-618700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-572400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-434300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-422700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-526000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-426200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-393000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-279700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-281200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-205000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-279000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-689200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-275000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-217300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-250100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-215600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-262200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-132800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-91900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-72400</v>
       </c>
-      <c r="AF26" s="3" t="s">
+      <c r="AG26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-60300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-109700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-149200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>321600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>88100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>426800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-565300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-933100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-579800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-617600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-573000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-433400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-422700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-523600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-420000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-393000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-281500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-283800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-207600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-281100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-690400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-276600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-218300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-250700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-215600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-262700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-132700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-92100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-73100</v>
       </c>
-      <c r="AF27" s="3" t="s">
+      <c r="AG27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-56000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-117900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-32900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>153900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>21400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>18700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-24200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>89600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>28900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-51000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-35900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-20600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>19100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>432700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-62900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-40800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>27800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>9600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>53200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-34300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3" t="s">
+      <c r="AG32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-109700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-149200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>321600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>88100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>426800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-565300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-933100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-579800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-617600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-573000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-433400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-422700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-523600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-420000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-393000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-281500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-283800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-207600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-281100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-690400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-276600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-218300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-250700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-215600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-262700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-132700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-92100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-73100</v>
       </c>
-      <c r="AF33" s="3" t="s">
+      <c r="AG33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-109700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-149200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>321600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>88100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>426800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-565300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-933100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-579800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-617600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-573000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-433400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-422700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-523600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-420000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-393000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-281500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-283800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-207600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-281100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-690400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-276600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-218300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-250700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-215600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-262700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-132700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-92100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-73100</v>
       </c>
-      <c r="AF35" s="3" t="s">
+      <c r="AG35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,172 +3524,176 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2460800</v>
+      </c>
+      <c r="E41" s="3">
         <v>2811100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3219900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3524400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6082700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6029900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6253400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6493200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7683700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9247800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11126200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4645400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5752600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6166900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3509000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3432800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2599700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3119000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2297200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2308100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2362500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1002800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1209200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1477100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1172400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1347400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>581500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>651100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>456800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>170100</v>
       </c>
-      <c r="AG41" s="3" t="s">
+      <c r="AH41" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2941000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2547600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2762700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2174900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>506400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>864300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1042300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1287500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1116900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>911300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>706000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>962100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>309700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>126100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>42300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>14700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>30500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>102300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>9400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>8900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>700</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
       <c r="Z42" s="3">
         <v>0</v>
       </c>
@@ -3611,10 +3701,10 @@
         <v>0</v>
       </c>
       <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>18000</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AD42" s="3" t="s">
         <v>11</v>
@@ -3622,679 +3712,703 @@
       <c r="AE42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="3" t="s">
+      <c r="AF42" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3280500</v>
+      </c>
+      <c r="E43" s="3">
         <v>3017600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2313000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2198800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2246600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2336000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2386500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2295000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2124600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1905400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1433700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1159100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>795400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>668400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>295900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>254600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>163600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>191800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>140500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>152700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>151500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>103000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>66500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>61000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>73100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>64100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>59200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>47900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>43200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>37800</v>
       </c>
-      <c r="AG43" s="3" t="s">
+      <c r="AH43" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>142300</v>
+      </c>
+      <c r="E44" s="3">
         <v>125400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>116300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>98500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>107300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>109700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>122400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>127200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>139700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>117500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>128700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>99500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>92700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>64200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>61700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>61200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>34200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>26900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>21400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>22500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>25900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>37700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>19600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>16900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>13400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>9800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>7300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3900</v>
       </c>
-      <c r="AG44" s="3" t="s">
+      <c r="AH44" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3556700</v>
+      </c>
+      <c r="E45" s="3">
         <v>3272200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3562000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3479200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3497300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3348200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2773300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2769200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2765100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2953500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2609100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2530900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2075600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1913400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1654200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1487700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1222600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>970100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>849300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>757500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>652000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>566500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>513100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>424200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>383400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>281500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>218800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>163600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>122800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>98100</v>
       </c>
-      <c r="AG45" s="3" t="s">
+      <c r="AH45" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12381300</v>
+      </c>
+      <c r="E46" s="3">
         <v>11773900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11973900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11475800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12440300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12688000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12577900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12972100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13829900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15135400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16003700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9397100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9025900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8939000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5563100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5251000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4050600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4410100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3317800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3249700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3192500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1710700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1808500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1979300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1642300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1720700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>866800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>868200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>628600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>309900</v>
       </c>
-      <c r="AG46" s="3" t="s">
+      <c r="AH46" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4044600</v>
+      </c>
+      <c r="E47" s="3">
         <v>4283100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3182600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3202100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1805500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1275300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1372000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1383900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1455900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1081800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>370600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>331900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>353500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>307600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>219100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>195200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>143200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>113800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>99100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>100400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>107100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>111000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>118200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>71000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>58500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>28200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>27100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>45100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>45100</v>
       </c>
-      <c r="AG47" s="3" t="s">
+      <c r="AH47" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2058500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2223700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2243800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2308400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2372400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2345700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2457200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2214700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2101500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1679600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1353300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>830200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>628600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>621000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>573400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>523500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>486900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>501600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>463100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>425900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>406300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>192400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>147400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>121900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>93900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>74300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>47900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>34100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>32400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>31100</v>
       </c>
-      <c r="AG48" s="3" t="s">
+      <c r="AH48" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>152900</v>
+      </c>
+      <c r="E49" s="3">
         <v>163600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>173400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>176300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>182300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>295200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>482100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>462300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>624000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>592100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>525400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>518500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>509300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>256100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>244000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>260500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>263300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>46000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>45900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>43800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>44900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>43800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>56600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>60500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>64600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>68300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>73000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>24300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>27200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>30000</v>
       </c>
-      <c r="AG49" s="3" t="s">
+      <c r="AH49" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>457800</v>
+      </c>
+      <c r="E52" s="3">
         <v>438900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>451400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>489700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>443400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>398600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>393200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>434700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>323400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>267000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>295700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>445400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>405300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>332000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>360900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>374100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>288900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>152700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>156000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>199200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>176100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>134700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>121800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>122600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>111100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>96700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>106400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>92500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>78900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>69700</v>
       </c>
-      <c r="AG52" s="3" t="s">
+      <c r="AH52" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19095000</v>
+      </c>
+      <c r="E54" s="3">
         <v>18883200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18025100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17652300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17243900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17002800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17282300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17467700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18334600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18756000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18548700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11523000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10922600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10455700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6960600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6604300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5232800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5224200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4081900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4019100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3927000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2192700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2252400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2355400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1970500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1988300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1121200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1064200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>812400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>485800</v>
       </c>
-      <c r="AG54" s="3" t="s">
+      <c r="AH54" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,135 +4968,139 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>280000</v>
+      </c>
+      <c r="E57" s="3">
         <v>342500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>267900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>219000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>212300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>258600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>289800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>239000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>287100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>213600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>232700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>179600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>152900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>121600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>118400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>96700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>51000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>69400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>48100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>32400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>38100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>37200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>25200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>33900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6000</v>
       </c>
-      <c r="AG57" s="3" t="s">
+      <c r="AH57" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2205000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2004700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1489000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1452600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1544400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1436000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>80200</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>100000</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>11</v>
@@ -4974,8 +5108,8 @@
       <c r="O58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4984,34 +5118,34 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>2400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>30700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>24000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>25800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>900</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-      <c r="AA58" s="3" t="s">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>2000</v>
       </c>
       <c r="AC58" s="3">
         <v>2000</v>
@@ -5023,393 +5157,408 @@
         <v>2000</v>
       </c>
       <c r="AF58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG58" s="3">
         <v>1900</v>
       </c>
-      <c r="AG58" s="3" t="s">
+      <c r="AH58" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6002200</v>
+      </c>
+      <c r="E59" s="3">
         <v>5821700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5274000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4904100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4903500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5241000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6681300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6500800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6567000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6862900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6188300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5704000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4924700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4514400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3654100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2890200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2375300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2262300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1979600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1663600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1371000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1148500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>921400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>744000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>738400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>627000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>438500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>323700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>276700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>255900</v>
       </c>
-      <c r="AG59" s="3" t="s">
+      <c r="AH59" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8487200</v>
+      </c>
+      <c r="E60" s="3">
         <v>8168900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7030800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6575700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6660200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6935700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7051400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6739800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6854100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7176400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6421000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5883600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5077600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4636100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3772500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2986900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2428600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2362400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2051700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1721800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1410100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1186500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>946500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>777900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>752300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>637700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>449800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>333800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>288100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>263800</v>
       </c>
-      <c r="AG60" s="3" t="s">
+      <c r="AH60" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2897300</v>
+      </c>
+      <c r="E61" s="3">
         <v>3069100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3439700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3391700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3340200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3338800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4148000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4177300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4175400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3475700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3503500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1282500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1757600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1840400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1920900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2109200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1374800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1356700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>446600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>439600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>582700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1062800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1116400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1145800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>745700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>727000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>674400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>624800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>355000</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>941600</v>
+      </c>
+      <c r="E62" s="3">
         <v>947600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>976500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1064600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1051800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>917500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1126800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1115800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1013800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>679500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>813800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>758000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>647000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>559000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>494400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>615700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>462400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>332500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>324100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>418800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>400200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>182800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>161300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>200200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>177900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>148500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>208100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>179600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>157100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>142600</v>
       </c>
-      <c r="AG62" s="3" t="s">
+      <c r="AH62" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12428000</v>
+      </c>
+      <c r="E66" s="3">
         <v>12289400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11557800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11140800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11150600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11287100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12385100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12094500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12073400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11357300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10761500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7962900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7518900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7072800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6219300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5750500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4312200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4061700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2829400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2585700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2397500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2435800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2227300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2126800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1681400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1519300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1340700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1138200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>800200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>406400</v>
       </c>
-      <c r="AG66" s="3" t="s">
+      <c r="AH66" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6094,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
-        <v>205100</v>
+        <v>0</v>
       </c>
       <c r="AD70" s="3">
         <v>205100</v>
@@ -6106,10 +6274,13 @@
         <v>205100</v>
       </c>
       <c r="AG70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+        <v>205100</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8606000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8582300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8472600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8323400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8645000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8733100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9159800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8594600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7661400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7195400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6577700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6004700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5571300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5148600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4625000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4205000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3812100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3530500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3246800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3039200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2758100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2067700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1791100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1572800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1322100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1106500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-843800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-670100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-578000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-505000</v>
       </c>
-      <c r="AG72" s="3" t="s">
+      <c r="AH72" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6667100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6593800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6467300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6511500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6093300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5715700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4897200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5373200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6261200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7398700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7787300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3560200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3403700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3382900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>741200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>853800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>920600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1162400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1252500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1433400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1529500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-243100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>25100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>228600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>289100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>469000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-424600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-279000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-192800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-125700</v>
       </c>
-      <c r="AG76" s="3" t="s">
+      <c r="AH76" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-109700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-149200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>321600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>88100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>426800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-565300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-933100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-579800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-617600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-573000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-433400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-422700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-523600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-420000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-393000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-281500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-283800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-207600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-281100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-690400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-276600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-218300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-250700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-215600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-262700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-132700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-92100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-73100</v>
       </c>
-      <c r="AF81" s="3" t="s">
+      <c r="AG81" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7047,20 +7246,20 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>11</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T83" s="3">
         <v>38200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>34600</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>11</v>
@@ -7074,32 +7273,35 @@
       <c r="Y83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>11</v>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE83" s="3">
         <v>9000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8800</v>
-      </c>
-      <c r="AF83" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>468500</v>
+      </c>
+      <c r="E89" s="3">
         <v>278800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>599800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>595500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>605500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>319700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-166300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-485500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-723700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-304800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>62700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>132400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>318300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>185400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>296000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>298100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-223700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-27800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>380800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-265300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-17800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-324400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>112300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-188800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-94400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-38200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-89800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-65400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-65800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-42100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-36500</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7747,20 +7968,20 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>11</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T91" s="3">
         <v>-50100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-42400</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>11</v>
@@ -7774,32 +7995,35 @@
       <c r="Y91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>11</v>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7400</v>
-      </c>
-      <c r="AF91" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-853800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1048600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-888300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3193900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-673800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>51500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-402100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-947500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1130700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1775500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-341900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1145500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-504300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-667400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>91300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-163700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-147100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-143700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-157700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>29400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-91300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-157100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-51100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-50100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>12900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-13400</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E100" s="3">
         <v>183400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>124500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>59200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-513700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>474000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>297600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>142400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>386000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6835200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>138800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>41600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2198600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>747700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>811600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-24800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1045000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>989800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-983100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1527900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-149800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>151700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>545300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>927400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>69500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>270000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>357000</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E101" s="3">
         <v>68300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-54200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-71600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>49500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>109100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-124900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-119700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-33000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>14500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-46300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>59000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>13000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>60500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-51800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>23200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>12900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-12900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-16800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>15300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-17300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-274300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-518000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-218100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2671100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>40500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-219200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1255100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1687800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6523100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-859700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-190800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2068300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>855400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1006400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-447300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>896700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1225800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1231900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1420700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-648000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>273600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>299300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-110600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>842800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-69600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>194300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>286700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-31900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-18000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3806900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3734300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3616600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3310200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3095700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3041100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3451600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3156000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2942600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2899600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3222100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2688900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2280500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1763600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1566600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1212200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>882000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>714900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>777200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>610100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>436200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>351900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>283200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>204900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>183800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>155000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>124600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>94100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>101500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>93900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>88500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2222100</v>
+      </c>
+      <c r="E9" s="3">
         <v>2180600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2091800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1868900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1644800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1624400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1754300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1928200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1852400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1729500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1911400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1680200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1349700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1118200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1032800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>804600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>681200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>508100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>512400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>407000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>338700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>312400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>291200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>199300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>175200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>146500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>101100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>83300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>75700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>66800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>63200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1584800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1553700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1524800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1441300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1450900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1416700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1697300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1227800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1090200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1170100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1310700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1008700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>930800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>645400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>533800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>407600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>200800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>206800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>264800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>203100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>97500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>39500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>23500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>10800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>25800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>27100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>25300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>298500</v>
+      </c>
+      <c r="E12" s="3">
         <v>304400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>279800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>280500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>283300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>320500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>244200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>421000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>370900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>340400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>286600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>231400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>172600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>141100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>109500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>104300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>75300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>63900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>48800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>43600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>35100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>28500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>26600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>17300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>12900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>8700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>5800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,37 +1338,40 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-27100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-38600</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>117900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-22000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>177300</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>11</v>
@@ -1368,8 +1388,8 @@
       <c r="Q14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1454,8 +1477,8 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>11</v>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>11</v>
@@ -1472,14 +1495,14 @@
       <c r="S15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U15" s="3">
         <v>11000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>10100</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>11</v>
@@ -1505,20 +1528,23 @@
       <c r="AD15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF15" s="3">
         <v>2100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2000</v>
-      </c>
-      <c r="AG15" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3719100</v>
+      </c>
+      <c r="E17" s="3">
         <v>3636100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3634600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3437900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2811800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2915900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2909000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3651600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3779300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3397600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3664200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3147400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2614600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2112100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1923900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1517600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1254800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>982600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1007300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>797600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>670700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>591100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>608200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>451100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>403300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>353100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>315700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>254800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>184000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>162000</v>
       </c>
-      <c r="AG17" s="3" t="s">
+      <c r="AH17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E18" s="3">
         <v>98200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-127700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>283900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>125200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>542600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-495600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-836700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-498000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-442100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-458500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-334100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-348500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-357300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-305400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-372800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-267700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-230100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-187500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-234500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-239200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-325000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-246200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-219500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-198100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-191100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-160700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-82500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-68100</v>
       </c>
-      <c r="AG18" s="3" t="s">
+      <c r="AH18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-52900</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,204 +1815,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-34900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>56000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>117900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>32900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-153900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-21400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-18700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>24200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-89600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-28900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>51000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>35900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>20600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-19100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-432700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>62900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>40800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-27800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-53200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>34300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3" t="s">
+      <c r="AH20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>144900</v>
+      </c>
+      <c r="E21" s="3">
         <v>165500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-76500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>393600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>278300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>384000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-476300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-844500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-402800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-258200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-420100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-331200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-287800</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T21" s="3">
         <v>-318400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-193600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-193500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-108900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-250100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-646400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-287600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-171100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-244000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-193200</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-73900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-59400</v>
-      </c>
-      <c r="AG21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1987,293 +2027,302 @@
         <v>9700</v>
       </c>
       <c r="E22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F22" s="3">
         <v>10100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>10400</v>
       </c>
       <c r="H22" s="3">
         <v>10400</v>
       </c>
       <c r="I22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J22" s="3">
         <v>10800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>52300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>37000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>22700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>34900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>45400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>43300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>24600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>17200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>10200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10100</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>9900</v>
       </c>
       <c r="Z22" s="3">
         <v>9900</v>
       </c>
       <c r="AA22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AB22" s="3">
         <v>3000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2300</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>139300</v>
+      </c>
+      <c r="E23" s="3">
         <v>53600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-81900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>391400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>147700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>377800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-504800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-869500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-504100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-513100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-471400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-359100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-371700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-481800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-379800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-365200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-256500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-245200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-177700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-263700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-682000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-272000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-215300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-250300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-216300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-253400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-134900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-89700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-70500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-68000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-56800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E24" s="3">
         <v>78800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>76900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>61700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>62200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-43500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>65300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>81800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>105600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>101000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>75200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>51000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>44200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>46400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>27800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>23200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>36000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>27400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>15300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-101800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-143500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>329200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>85800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>421300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-570100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-934200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-585900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-618700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-572400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-434300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-422700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-526000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-426200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-393000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-279700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-281200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-205000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-279000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-689200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-275000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-217300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-250100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-215600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-262200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-132800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-91900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-72400</v>
       </c>
-      <c r="AG26" s="3" t="s">
+      <c r="AH26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-60300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-109700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-149200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>321600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>88100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>426800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-565300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-933100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-579800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-617600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-573000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-433400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-422700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-523600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-420000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-393000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-281500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-283800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-207600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-281100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-690400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-276600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-218300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-250700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-215600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-262700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-132700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-92100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-73100</v>
       </c>
-      <c r="AG27" s="3" t="s">
+      <c r="AH27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="E32" s="3">
         <v>34900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-56000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-117900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-32900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>153900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>21400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>18700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-24200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>89600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>28900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-51000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-35900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-20600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>19100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>432700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-62900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>27800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>9600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>53200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-34300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3" t="s">
+      <c r="AH32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-109700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-149200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>321600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>88100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>426800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-565300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-933100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-579800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-617600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-573000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-433400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-422700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-523600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-420000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-393000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-281500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-283800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-207600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-281100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-690400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-276600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-218300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-250700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-215600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-262700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-132700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-92100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-73100</v>
       </c>
-      <c r="AG33" s="3" t="s">
+      <c r="AH33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-109700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-149200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>321600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>88100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>426800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-565300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-933100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-579800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-617600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-573000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-433400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-422700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-523600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-420000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-393000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-281500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-283800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-207600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-281100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-690400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-276600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-218300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-250700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-215600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-262700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-132700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-92100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-73100</v>
       </c>
-      <c r="AG35" s="3" t="s">
+      <c r="AH35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,178 +3611,182 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2646500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2460800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2811100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3219900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3524400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6082700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6029900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6253400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6493200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7683700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9247800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11126200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4645400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5752600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6166900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3509000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3432800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2599700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3119000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2297200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2308100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2362500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1002800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1209200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1477100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1172400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1347400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>581500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>651100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>456800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>170100</v>
       </c>
-      <c r="AH41" s="3" t="s">
+      <c r="AI41" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3387500</v>
+      </c>
+      <c r="E42" s="3">
         <v>2941000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2547600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2762700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2174900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>506400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>864300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1042300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1287500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1116900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>911300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>706000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>962100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>309700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>126100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>42300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>30500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>102300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>9400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>8900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>700</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
-      </c>
       <c r="AA42" s="3">
         <v>0</v>
       </c>
@@ -3704,10 +3794,10 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>18000</v>
-      </c>
-      <c r="AD42" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>11</v>
@@ -3715,700 +3805,724 @@
       <c r="AF42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="3" t="s">
+      <c r="AG42" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3464200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3280500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3017600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2313000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2198800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2246600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2336000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2386500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2295000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2124600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1905400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1433700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1159100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>795400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>668400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>295900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>254600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>163600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>191800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>140500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>152700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>151500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>103000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>66500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>61000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>73100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>64100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>59200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>47900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>43200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>37800</v>
       </c>
-      <c r="AH43" s="3" t="s">
+      <c r="AI43" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>157500</v>
+      </c>
+      <c r="E44" s="3">
         <v>142300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>125400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>116300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>98500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>107300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>109700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>122400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>127200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>139700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>117500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>128700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>99500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>92700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>64200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>61700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>61200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>34200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>26900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>21400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>22500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>25900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>37700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>19600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>16900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>13400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>9800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>7300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3900</v>
       </c>
-      <c r="AH44" s="3" t="s">
+      <c r="AI44" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3225000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3556700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3272200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3562000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3479200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3497300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3348200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2773300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2769200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2765100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2953500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2609100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2530900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2075600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1913400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1654200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1487700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1222600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>970100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>849300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>757500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>652000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>566500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>513100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>424200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>383400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>281500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>218800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>163600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>122800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>98100</v>
       </c>
-      <c r="AH45" s="3" t="s">
+      <c r="AI45" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12880700</v>
+      </c>
+      <c r="E46" s="3">
         <v>12381300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11773900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11973900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11475800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12440300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12688000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12577900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12972100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13829900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15135400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16003700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9397100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9025900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8939000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5563100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5251000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4050600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4410100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3317800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3249700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3192500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1710700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1808500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1979300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1642300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1720700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>866800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>868200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>628600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>309900</v>
       </c>
-      <c r="AH46" s="3" t="s">
+      <c r="AI46" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3820600</v>
+      </c>
+      <c r="E47" s="3">
         <v>4044600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4283100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3182600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3202100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1805500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1275300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1372000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1383900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1455900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1081800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>370600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>331900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>353500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>307600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>219100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>195200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>143200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>113800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>99100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>100400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>107100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>111000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>118200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>71000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>58500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>28200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>27100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>45400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>45100</v>
       </c>
-      <c r="AH47" s="3" t="s">
+      <c r="AI47" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2188700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2058500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2223700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2243800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2308400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2372400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2345700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2457200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2214700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2101500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1679600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1353300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>830200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>628600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>621000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>573400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>523500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>486900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>501600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>463100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>425900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>406300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>192400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>147400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>121900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>93900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>74300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>47900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>34100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>32400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>31100</v>
       </c>
-      <c r="AH48" s="3" t="s">
+      <c r="AI48" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>142100</v>
+      </c>
+      <c r="E49" s="3">
         <v>152900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>163600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>173400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>176300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>182300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>295200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>482100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>462300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>624000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>592100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>525400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>518500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>509300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>256100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>244000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>260500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>263300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>46000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>45900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>43800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>44900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>43800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>56600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>60500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>64600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>68300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>73000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>24300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>27200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>30000</v>
       </c>
-      <c r="AH49" s="3" t="s">
+      <c r="AI49" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>537900</v>
+      </c>
+      <c r="E52" s="3">
         <v>457800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>438900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>451400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>489700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>443400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>398600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>393200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>434700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>323400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>267000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>295700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>445400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>405300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>332000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>360900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>374100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>288900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>152700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>156000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>199200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>176100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>134700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>121800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>122600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>111100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>96700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>106400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>92500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>78900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>69700</v>
       </c>
-      <c r="AH52" s="3" t="s">
+      <c r="AI52" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19570000</v>
+      </c>
+      <c r="E54" s="3">
         <v>19095000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18883200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18025100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17652300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17243900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17002800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17282300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17467700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18334600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18756000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18548700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11523000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10922600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10455700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6960600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6604300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5232800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5224200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4081900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4019100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3927000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2192700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2252400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2355400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1970500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1988300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1121200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1064200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>812400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>485800</v>
       </c>
-      <c r="AH54" s="3" t="s">
+      <c r="AI54" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,141 +5099,145 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>293700</v>
+      </c>
+      <c r="E57" s="3">
         <v>280000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>342500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>267900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>219000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>212300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>258600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>289800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>239000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>287100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>213600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>232700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>179600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>152900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>121600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>118400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>96700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>51000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>69400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>48100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>32400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>38100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>37200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>25200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>33900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6000</v>
       </c>
-      <c r="AH57" s="3" t="s">
+      <c r="AI57" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2366500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2205000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2004700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1489000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1452600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1544400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1436000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>80200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>100000</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>11</v>
@@ -5111,8 +5245,8 @@
       <c r="P58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5121,34 +5255,34 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>2400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>30700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>24000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>25800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>900</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-      <c r="AB58" s="3" t="s">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>2000</v>
       </c>
       <c r="AD58" s="3">
         <v>2000</v>
@@ -5160,405 +5294,420 @@
         <v>2000</v>
       </c>
       <c r="AG58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH58" s="3">
         <v>1900</v>
       </c>
-      <c r="AH58" s="3" t="s">
+      <c r="AI58" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5957000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6002200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5821700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5274000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4904100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4903500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5241000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6681300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6500800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6567000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6862900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6188300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5704000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4924700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4514400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3654100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2890200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2375300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2262300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1979600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1663600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1371000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1148500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>921400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>744000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>738400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>627000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>438500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>323700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>276700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>255900</v>
       </c>
-      <c r="AH59" s="3" t="s">
+      <c r="AI59" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8617200</v>
+      </c>
+      <c r="E60" s="3">
         <v>8487200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8168900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7030800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6575700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6660200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6935700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7051400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6739800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6854100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7176400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6421000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5883600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5077600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4636100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3772500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2986900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2428600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2362400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2051700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1721800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1410100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1186500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>946500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>777900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>752300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>637700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>449800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>333800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>288100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>263800</v>
       </c>
-      <c r="AH60" s="3" t="s">
+      <c r="AI60" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2861300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2897300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3069100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3439700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3391700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3340200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3338800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4148000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4177300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4175400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3475700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3503500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1282500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1757600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1840400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1920900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2109200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1374800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1356700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>446600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>439600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>582700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1062800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1116400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1145800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>745700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>727000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>674400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>624800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>355000</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1125300</v>
+      </c>
+      <c r="E62" s="3">
         <v>941600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>947600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>976500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1064600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1051800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>917500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1126800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1115800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1013800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>679500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>813800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>758000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>647000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>559000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>494400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>615700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>462400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>332500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>324100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>418800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>400200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>182800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>161300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>200200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>177900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>148500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>208100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>179600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>157100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>142600</v>
       </c>
-      <c r="AH62" s="3" t="s">
+      <c r="AI62" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12702700</v>
+      </c>
+      <c r="E66" s="3">
         <v>12428000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12289400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11557800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11140800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11150600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11287100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12385100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12094500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12073400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11357300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10761500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7962900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7518900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7072800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6219300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5750500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4312200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4061700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2829400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2585700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2397500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2435800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2227300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2126800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1681400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1519300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1340700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1138200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>800200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>406400</v>
       </c>
-      <c r="AH66" s="3" t="s">
+      <c r="AI66" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6265,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
-        <v>205100</v>
+        <v>0</v>
       </c>
       <c r="AE70" s="3">
         <v>205100</v>
@@ -6277,10 +6445,13 @@
         <v>205100</v>
       </c>
       <c r="AH70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+        <v>205100</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8524100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8606000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8582300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8472600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8323400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8645000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8733100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9159800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8594600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7661400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7195400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6577700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6004700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5571300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5148600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4625000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4205000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3812100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3530500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3246800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3039200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2758100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2067700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1791100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1572800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1322100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1106500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-843800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-670100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-578000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-505000</v>
       </c>
-      <c r="AH72" s="3" t="s">
+      <c r="AI72" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6867300</v>
+      </c>
+      <c r="E76" s="3">
         <v>6667100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6593800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6467300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6511500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6093300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5715700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4897200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5373200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6261200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7398700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7787300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3560200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3403700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3382900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>741200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>853800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>920600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1162400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1252500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1433400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1529500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-243100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>25100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>228600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>289100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>469000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-424600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-279000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-192800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-125700</v>
       </c>
-      <c r="AH76" s="3" t="s">
+      <c r="AI76" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-109700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-149200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>321600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>88100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>426800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-565300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-933100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-579800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-617600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-573000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-433400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-422700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-523600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-420000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-393000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-281500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-283800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-207600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-281100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-690400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-276600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-218300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-250700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-215600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-262700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-132700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-92100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-73100</v>
       </c>
-      <c r="AG81" s="3" t="s">
+      <c r="AH81" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7249,20 +7448,20 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>11</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U83" s="3">
         <v>38200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>34600</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>11</v>
@@ -7276,32 +7475,35 @@
       <c r="Z83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>11</v>
+      <c r="AC83" s="3">
+        <v>0</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF83" s="3">
         <v>9000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8800</v>
-      </c>
-      <c r="AG83" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>617900</v>
+      </c>
+      <c r="E89" s="3">
         <v>468500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>278800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>599800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>595500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>605500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>319700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-166300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-485500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-723700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-304800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>62700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>132400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>318300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>185400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>296000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>298100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-223700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-27800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>380800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-265300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-324400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>112300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-188800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-94400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-38200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-89800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-65400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-65800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-42100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-36500</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7971,20 +8192,20 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>11</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U91" s="3">
         <v>-50100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-42400</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>11</v>
@@ -7998,32 +8219,35 @@
       <c r="Z91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>11</v>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7400</v>
-      </c>
-      <c r="AG91" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-709900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-853800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1048600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-888300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3193900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-673800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>51500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-402100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-947500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1130700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1775500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-341900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1145500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-504300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-667400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>91300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-163700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-147100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-143700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-157700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>29400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-91300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-157100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-40000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-51100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-50100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>12900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-13400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E100" s="3">
         <v>183800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>183400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>124500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>59200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-513700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>474000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>297600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>142400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>386000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6835200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>138800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>41600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2198600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>747700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>811600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-24800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1045000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>989800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-983100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1527900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-149800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>151700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>545300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>927400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>69500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>270000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>357000</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-72800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>68300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-54200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-71600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>49500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>109100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-124900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-119700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-33000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>14500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-46300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>59000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>13000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>60500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-51800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>23200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>12900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-12900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-16800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>15300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-17300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>105700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-274300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-518000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-218100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2671100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-33400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-219200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1255100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1687800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6523100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-859700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-190800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2068300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>855400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1006400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-447300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>896700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1225800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1231900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1420700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-648000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>273600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>299300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-110600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>842800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-69600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>194300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>286700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-31900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-18000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>SE</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4328200</v>
+      </c>
+      <c r="E8" s="3">
         <v>3806900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3734300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3616600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3310200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3095700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3041100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3451600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3156000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2942600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2899600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3222100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2688900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2280500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1763600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1566600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1212200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>882000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>714900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>777200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>610100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>436200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>351900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>283200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>204900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>183800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>155000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>124600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>94100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>101500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>93900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>88500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2467200</v>
+      </c>
+      <c r="E9" s="3">
         <v>2222100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2180600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2091800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1868900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1644800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1624400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1754300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1928200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1852400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1729500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1911400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1680200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1349700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1118200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1032800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>804600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>681200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>508100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>512400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>407000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>338700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>312400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>291200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>199300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>175200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>146500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>101100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>83300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>75700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>66800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>63200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1861100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1584800</v>
       </c>
-      <c r="E10" s="3">
-        <v>1553700</v>
-      </c>
       <c r="F10" s="3">
+        <v>1553800</v>
+      </c>
+      <c r="G10" s="3">
         <v>1524800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1441300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1450900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1416700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1697300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1227800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1090200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1170100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1310700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1008700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>930800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>645400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>533800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>407600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>200800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>206800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>264800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>203100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>97500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>39500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>23500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>10800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>25800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>27100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>25300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E12" s="3">
         <v>298500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>304400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>279800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>280500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>283300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>320500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>244200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>421000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>370900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>340400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>286600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>231400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>172600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>141100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>109500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>104300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>75300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>63900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>48800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>43600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>35100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>28500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>26600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>17300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>10700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>8700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,41 +1358,44 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-27100</v>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F14" s="3">
-        <v>-38600</v>
+        <v>84100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>117900</v>
+        <v>41700</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="J14" s="3">
+        <v>145600</v>
+      </c>
+      <c r="K14" s="3">
         <v>-22000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>177300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1391,8 +1411,8 @@
       <c r="R14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>110200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>102300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>102300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>101500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>107100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>120200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>120200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1480,8 +1503,8 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>11</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>11</v>
@@ -1498,15 +1521,15 @@
       <c r="T15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V15" s="3">
         <v>11000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>10100</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1531,20 +1554,23 @@
       <c r="AE15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG15" s="3">
         <v>2100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2000</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AI15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3719100</v>
+        <v>4125800</v>
       </c>
       <c r="E17" s="3">
-        <v>3636100</v>
+        <v>3724000</v>
       </c>
       <c r="F17" s="3">
-        <v>3634600</v>
+        <v>3663200</v>
       </c>
       <c r="G17" s="3">
+        <v>3673100</v>
+      </c>
+      <c r="H17" s="3">
         <v>3437900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2811800</v>
       </c>
-      <c r="I17" s="3">
-        <v>2915900</v>
-      </c>
       <c r="J17" s="3">
+        <v>2798000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2909000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3651600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3779300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3397600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3664200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3147400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2614600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2112100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1923900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1517600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1254800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>982600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1007300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>797600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>670700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>591100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>608200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>451100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>403300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>353100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>315700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>254800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>184000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>162000</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>87800</v>
+        <v>202400</v>
       </c>
       <c r="E18" s="3">
-        <v>98200</v>
+        <v>82900</v>
       </c>
       <c r="F18" s="3">
-        <v>-18000</v>
+        <v>71100</v>
       </c>
       <c r="G18" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="H18" s="3">
         <v>-127700</v>
       </c>
-      <c r="H18" s="3">
-        <v>283900</v>
-      </c>
       <c r="I18" s="3">
-        <v>125200</v>
+        <v>283800</v>
       </c>
       <c r="J18" s="3">
+        <v>243100</v>
+      </c>
+      <c r="K18" s="3">
         <v>542600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-495600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-836700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-498000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-442100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-458500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-334100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-348500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-357300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-305400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-372800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-267700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-230100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-187500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-234500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-239200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-325000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-246200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-219500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-198100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-191100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-160700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-82500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-68100</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-52900</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>61200</v>
+        <v>-43500</v>
       </c>
       <c r="E20" s="3">
-        <v>-34900</v>
+        <v>-57600</v>
       </c>
       <c r="F20" s="3">
-        <v>3300</v>
+        <v>8600</v>
       </c>
       <c r="G20" s="3">
-        <v>56000</v>
+        <v>17300</v>
       </c>
       <c r="H20" s="3">
-        <v>117900</v>
+        <v>-45400</v>
       </c>
       <c r="I20" s="3">
-        <v>32900</v>
+        <v>-109400</v>
       </c>
       <c r="J20" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K20" s="3">
         <v>-153900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-21400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-18700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>24200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-89600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-28900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>51000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>35900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>20600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-19100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-432700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>62900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>40800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-27800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-53200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>34300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>144900</v>
+        <v>356100</v>
       </c>
       <c r="E21" s="3">
-        <v>165500</v>
+        <v>242800</v>
       </c>
       <c r="F21" s="3">
-        <v>-20400</v>
+        <v>164800</v>
       </c>
       <c r="G21" s="3">
-        <v>-76500</v>
+        <v>27700</v>
       </c>
       <c r="H21" s="3">
-        <v>393600</v>
+        <v>24800</v>
       </c>
       <c r="I21" s="3">
-        <v>278300</v>
+        <v>513400</v>
       </c>
       <c r="J21" s="3">
+        <v>356600</v>
+      </c>
+      <c r="K21" s="3">
         <v>384000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-476300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-844500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-402800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-258200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-420100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-331200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-287800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U21" s="3">
         <v>-318400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-193600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-193500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-108900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-250100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-646400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-287600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-171100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-244000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-193200</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-73900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-59400</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="3">
         <v>9700</v>
       </c>
-      <c r="E22" s="3">
-        <v>9700</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K22" s="3">
+        <v>10800</v>
+      </c>
+      <c r="L22" s="3">
+        <v>11600</v>
+      </c>
+      <c r="M22" s="3">
+        <v>11400</v>
+      </c>
+      <c r="N22" s="3">
+        <v>11600</v>
+      </c>
+      <c r="O22" s="3">
+        <v>52300</v>
+      </c>
+      <c r="P22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="R22" s="3">
+        <v>26900</v>
+      </c>
+      <c r="S22" s="3">
+        <v>34900</v>
+      </c>
+      <c r="T22" s="3">
+        <v>45400</v>
+      </c>
+      <c r="U22" s="3">
+        <v>43300</v>
+      </c>
+      <c r="V22" s="3">
+        <v>24600</v>
+      </c>
+      <c r="W22" s="3">
+        <v>17200</v>
+      </c>
+      <c r="X22" s="3">
+        <v>10800</v>
+      </c>
+      <c r="Y22" s="3">
         <v>10200</v>
       </c>
-      <c r="H22" s="3">
-        <v>10400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>10400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>10800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>11600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>11400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>11600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>52300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>37000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>22700</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>26900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>34900</v>
-      </c>
-      <c r="S22" s="3">
-        <v>45400</v>
-      </c>
-      <c r="T22" s="3">
-        <v>43300</v>
-      </c>
-      <c r="U22" s="3">
-        <v>24600</v>
-      </c>
-      <c r="V22" s="3">
-        <v>17200</v>
-      </c>
-      <c r="W22" s="3">
-        <v>10800</v>
-      </c>
-      <c r="X22" s="3">
-        <v>10200</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10100</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>9900</v>
       </c>
       <c r="AA22" s="3">
         <v>9900</v>
       </c>
       <c r="AB22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AC22" s="3">
         <v>3000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>6700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2300</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>139300</v>
+        <v>245900</v>
       </c>
       <c r="E23" s="3">
-        <v>53600</v>
+        <v>140500</v>
       </c>
       <c r="F23" s="3">
-        <v>-24900</v>
+        <v>55800</v>
       </c>
       <c r="G23" s="3">
-        <v>-81900</v>
+        <v>-34700</v>
       </c>
       <c r="H23" s="3">
-        <v>391400</v>
+        <v>-82300</v>
       </c>
       <c r="I23" s="3">
-        <v>147700</v>
+        <v>393200</v>
       </c>
       <c r="J23" s="3">
+        <v>149200</v>
+      </c>
+      <c r="K23" s="3">
         <v>377800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-504800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-869500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-504100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-513100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-471400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-359100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-371700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-481800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-379800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-365200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-256500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-245200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-177700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-263700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-682000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-272000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-215300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-250300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-216300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-253400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-134900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-89700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-70500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-68000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-56800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>92600</v>
+      </c>
+      <c r="E24" s="3">
         <v>60600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>78800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>76900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>61700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>62200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>61900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-43500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>65300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>64800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>81800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>105600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>101000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>75200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>51000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>44200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>46400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>27800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>23200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>36000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>27400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>15300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>78700</v>
+        <v>153300</v>
       </c>
       <c r="E26" s="3">
-        <v>-25200</v>
+        <v>79900</v>
       </c>
       <c r="F26" s="3">
-        <v>-101800</v>
+        <v>-23000</v>
       </c>
       <c r="G26" s="3">
-        <v>-143500</v>
+        <v>-111600</v>
       </c>
       <c r="H26" s="3">
-        <v>329200</v>
+        <v>-144000</v>
       </c>
       <c r="I26" s="3">
-        <v>85800</v>
+        <v>331000</v>
       </c>
       <c r="J26" s="3">
+        <v>87300</v>
+      </c>
+      <c r="K26" s="3">
         <v>421300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-570100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-934200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-585900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-618700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-572400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-434300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-422700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-526000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-426200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-393000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-279700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-281200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-205000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-279000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-689200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-275000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-217300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-250100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-215600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-262200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-132800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-91900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-72400</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-60300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>81900</v>
+        <v>153300</v>
       </c>
       <c r="E27" s="3">
+        <v>79900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-23700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-109700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-149200</v>
-      </c>
       <c r="H27" s="3">
-        <v>321600</v>
+        <v>-144000</v>
       </c>
       <c r="I27" s="3">
+        <v>331000</v>
+      </c>
+      <c r="J27" s="3">
         <v>88100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>426800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-565300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-933100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-579800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-617600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-573000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-433400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-422700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-523600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-420000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-393000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-281500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-283800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-207600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-281100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-690400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-276600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-218300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-250700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-215600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-262700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-132700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-92100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-73100</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-61200</v>
+        <v>43500</v>
       </c>
       <c r="E32" s="3">
-        <v>34900</v>
+        <v>57600</v>
       </c>
       <c r="F32" s="3">
-        <v>-3300</v>
+        <v>-8600</v>
       </c>
       <c r="G32" s="3">
-        <v>-56000</v>
+        <v>-17300</v>
       </c>
       <c r="H32" s="3">
-        <v>-117900</v>
+        <v>45400</v>
       </c>
       <c r="I32" s="3">
-        <v>-32900</v>
+        <v>109400</v>
       </c>
       <c r="J32" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="K32" s="3">
         <v>153900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>21400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>18700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-24200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>89600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>28900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-51000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-35900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-20600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>19100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>432700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-62900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>27800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>9600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>53200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-34300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>81900</v>
+        <v>153300</v>
       </c>
       <c r="E33" s="3">
+        <v>79900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-23700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-109700</v>
       </c>
-      <c r="G33" s="3">
-        <v>-149200</v>
-      </c>
       <c r="H33" s="3">
-        <v>321600</v>
+        <v>-144000</v>
       </c>
       <c r="I33" s="3">
+        <v>331000</v>
+      </c>
+      <c r="J33" s="3">
         <v>88100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>426800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-565300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-933100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-579800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-617600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-573000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-433400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-422700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-523600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-420000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-393000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-281500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-283800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-207600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-281100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-690400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-276600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-218300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-250700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-215600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-262700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-132700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-92100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-73100</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>81900</v>
+        <v>153300</v>
       </c>
       <c r="E35" s="3">
+        <v>79900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-23700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-109700</v>
       </c>
-      <c r="G35" s="3">
-        <v>-149200</v>
-      </c>
       <c r="H35" s="3">
-        <v>321600</v>
+        <v>-144000</v>
       </c>
       <c r="I35" s="3">
+        <v>331000</v>
+      </c>
+      <c r="J35" s="3">
         <v>88100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>426800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-565300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-933100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-579800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-617600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-573000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-433400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-422700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-523600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-420000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-393000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-281500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-283800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-207600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-281100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-690400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-276600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-218300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-250700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-215600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-262700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-132700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-92100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-73100</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,184 +3698,188 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2538700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2646500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2460800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2811100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3219900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3524400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6082700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6029900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6253400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6493200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7683700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9247800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11126200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4645400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5752600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6166900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3509000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3432800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2599700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3119000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2297200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2308100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2362500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1002800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1209200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1477100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1172400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1347400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>581500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>651100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>456800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>170100</v>
       </c>
-      <c r="AI41" s="3" t="s">
+      <c r="AJ41" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5374500</v>
+      </c>
+      <c r="E42" s="3">
         <v>3387500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2941000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2547600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2762700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2174900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>506400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>864300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1042300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1287500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1116900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>911300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>706000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>962100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>309700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>126100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>42300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>14700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>30500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>102300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>9400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>8900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>700</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
       <c r="AB42" s="3">
         <v>0</v>
       </c>
@@ -3797,732 +3887,756 @@
         <v>0</v>
       </c>
       <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
         <v>18000</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AG42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="3" t="s">
+      <c r="AH42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4227800</v>
+      </c>
+      <c r="E43" s="3">
         <v>3464200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3280500</v>
       </c>
-      <c r="F43" s="3">
-        <v>3017600</v>
-      </c>
       <c r="G43" s="3">
+        <v>4538700</v>
+      </c>
+      <c r="H43" s="3">
         <v>2313000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2198800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2246600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2336000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2386500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2295000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2124600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1905400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1433700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1159100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>795400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>668400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>295900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>254600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>163600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>191800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>140500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>152700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>151500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>103000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>66500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>61000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>73100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>64100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>59200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>47900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>43200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>37800</v>
       </c>
-      <c r="AI43" s="3" t="s">
+      <c r="AJ43" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>200700</v>
+      </c>
+      <c r="E44" s="3">
         <v>157500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>142300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>125400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>116300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>98500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>107300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>109700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>122400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>127200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>139700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>117500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>128700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>99500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>92700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>64200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>61700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>61200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>34200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>26900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>21400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>22500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>25900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>37700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>19600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>16900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>13400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>9800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>7300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3900</v>
       </c>
-      <c r="AI44" s="3" t="s">
+      <c r="AJ44" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3225000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3556700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3272200</v>
+      <c r="D45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="G45" s="3">
-        <v>3562000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3479200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3497300</v>
-      </c>
-      <c r="J45" s="3">
+        <v>228800</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K45" s="3">
         <v>3348200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2773300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2769200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2765100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2953500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2609100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2530900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2075600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1913400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1654200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1487700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1222600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>970100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>849300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>757500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>652000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>566500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>513100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>424200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>383400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>281500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>218800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>163600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>122800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>98100</v>
       </c>
-      <c r="AI45" s="3" t="s">
+      <c r="AJ45" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15554200</v>
+      </c>
+      <c r="E46" s="3">
         <v>12880700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12381300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11773900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11973900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11475800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12440300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12688000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12577900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12972100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13829900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15135400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16003700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9397100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9025900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8939000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5563100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5251000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4050600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4410100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3317800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3249700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3192500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1710700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1808500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1979300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1642300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1720700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>866800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>868200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>628600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>309900</v>
       </c>
-      <c r="AI46" s="3" t="s">
+      <c r="AJ46" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3820600</v>
+        <v>2974600</v>
       </c>
       <c r="E47" s="3">
-        <v>4044600</v>
+        <v>3769500</v>
       </c>
       <c r="F47" s="3">
-        <v>4283100</v>
+        <v>4024600</v>
       </c>
       <c r="G47" s="3">
-        <v>3182600</v>
+        <v>4262600</v>
       </c>
       <c r="H47" s="3">
-        <v>3202100</v>
+        <v>3162700</v>
       </c>
       <c r="I47" s="3">
-        <v>1805500</v>
+        <v>3183300</v>
       </c>
       <c r="J47" s="3">
+        <v>1789200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1275300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1372000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1383900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1455900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1081800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>370600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>331900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>353500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>307600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>219100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>195200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>143200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>113800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>99100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>100400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>107100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>111000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>118200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>71000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>58500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>28200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>27100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>45100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>45400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>45100</v>
       </c>
-      <c r="AI47" s="3" t="s">
+      <c r="AJ47" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2327700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2188700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2058500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2223700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2243800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2308400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2372400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2345700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2457200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2214700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2101500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1679600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1353300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>830200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>628600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>621000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>573400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>523500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>486900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>501600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>463100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>425900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>406300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>192400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>147400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>121900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>93900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>74300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>47900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>34100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>32400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>31100</v>
       </c>
-      <c r="AI48" s="3" t="s">
+      <c r="AJ48" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>144600</v>
+      </c>
+      <c r="E49" s="3">
         <v>142100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>152900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>163600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>173400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>176300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>182300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>295200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>482100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>462300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>624000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>592100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>525400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>518500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>509300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>256100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>244000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>260500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>263300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>46000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>45900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>43800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>44900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>43800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>56600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>60500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>64600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>68300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>73000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>24300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>27200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>30000</v>
       </c>
-      <c r="AI49" s="3" t="s">
+      <c r="AJ49" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>537900</v>
+        <v>146000</v>
       </c>
       <c r="E52" s="3">
-        <v>457800</v>
+        <v>136000</v>
       </c>
       <c r="F52" s="3">
-        <v>438900</v>
+        <v>127200</v>
       </c>
       <c r="G52" s="3">
-        <v>451400</v>
+        <v>97900</v>
       </c>
       <c r="H52" s="3">
-        <v>489700</v>
+        <v>140400</v>
       </c>
       <c r="I52" s="3">
-        <v>443400</v>
+        <v>164600</v>
       </c>
       <c r="J52" s="3">
+        <v>160600</v>
+      </c>
+      <c r="K52" s="3">
         <v>398600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>393200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>434700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>323400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>267000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>295700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>445400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>405300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>332000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>360900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>374100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>288900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>152700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>156000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>199200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>176100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>134700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>121800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>122600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>111100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>96700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>106400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>92500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>78900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>69700</v>
       </c>
-      <c r="AI52" s="3" t="s">
+      <c r="AJ52" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21691700</v>
+      </c>
+      <c r="E54" s="3">
         <v>19570000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19095000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18883200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18025100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17652300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17243900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17002800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17282300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17467700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18334600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18756000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18548700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11523000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10922600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10455700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6960600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6604300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5232800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5224200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4081900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4019100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3927000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2192700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2252400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2355400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1970500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1988300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1121200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1064200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>812400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>485800</v>
       </c>
-      <c r="AI54" s="3" t="s">
+      <c r="AJ54" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,156 +5230,160 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>274800</v>
+      </c>
+      <c r="E57" s="3">
         <v>293700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>280000</v>
       </c>
-      <c r="F57" s="3">
-        <v>342500</v>
-      </c>
       <c r="G57" s="3">
+        <v>406000</v>
+      </c>
+      <c r="H57" s="3">
         <v>267900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>219000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>212300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>258600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>289800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>239000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>287100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>213600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>232700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>179600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>152900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>121600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>118400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>96700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>51000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>69400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>48100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>32400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>38100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>37200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>25200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>33900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6000</v>
       </c>
-      <c r="AI57" s="3" t="s">
+      <c r="AJ57" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2366500</v>
+        <v>610300</v>
       </c>
       <c r="E58" s="3">
-        <v>2205000</v>
+        <v>518400</v>
       </c>
       <c r="F58" s="3">
-        <v>2004700</v>
+        <v>529700</v>
       </c>
       <c r="G58" s="3">
-        <v>1489000</v>
+        <v>592900</v>
       </c>
       <c r="H58" s="3">
-        <v>1452600</v>
+        <v>380200</v>
       </c>
       <c r="I58" s="3">
-        <v>1544400</v>
+        <v>382800</v>
       </c>
       <c r="J58" s="3">
+        <v>406100</v>
+      </c>
+      <c r="K58" s="3">
         <v>1436000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>80200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>100000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -5258,34 +5392,34 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>2400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>30700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>24000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>25800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>900</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>2000</v>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AE58" s="3">
         <v>2000</v>
@@ -5297,417 +5431,432 @@
         <v>2000</v>
       </c>
       <c r="AH58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AI58" s="3">
         <v>1900</v>
       </c>
-      <c r="AI58" s="3" t="s">
+      <c r="AJ58" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5957000</v>
+        <v>6556000</v>
       </c>
       <c r="E59" s="3">
-        <v>6002200</v>
+        <v>6000900</v>
       </c>
       <c r="F59" s="3">
-        <v>5821700</v>
+        <v>5861600</v>
       </c>
       <c r="G59" s="3">
-        <v>5274000</v>
+        <v>5536800</v>
       </c>
       <c r="H59" s="3">
-        <v>4904100</v>
+        <v>4785700</v>
       </c>
       <c r="I59" s="3">
-        <v>4903500</v>
+        <v>4564500</v>
       </c>
       <c r="J59" s="3">
+        <v>4760800</v>
+      </c>
+      <c r="K59" s="3">
         <v>5241000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6681300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6500800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6567000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6862900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6188300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5704000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4924700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4514400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3654100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2890200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2375300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2262300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1979600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1663600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1371000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1148500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>921400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>744000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>738400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>627000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>438500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>323700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>276700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>255900</v>
       </c>
-      <c r="AI59" s="3" t="s">
+      <c r="AJ59" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9589400</v>
+      </c>
+      <c r="E60" s="3">
         <v>8617200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8487200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8168900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7030800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6575700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6660200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6935700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7051400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6739800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6854100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7176400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6421000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5883600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5077600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4636100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3772500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2986900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2428600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2362400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2051700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1721800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1410100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1186500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>946500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>777900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>752300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>637700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>449800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>333800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>288100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>263800</v>
       </c>
-      <c r="AI60" s="3" t="s">
+      <c r="AJ60" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2861300</v>
+        <v>3793400</v>
       </c>
       <c r="E61" s="3">
-        <v>2897300</v>
+        <v>3724200</v>
       </c>
       <c r="F61" s="3">
-        <v>3069100</v>
+        <v>3629300</v>
       </c>
       <c r="G61" s="3">
-        <v>3439700</v>
+        <v>3869500</v>
       </c>
       <c r="H61" s="3">
-        <v>3391700</v>
+        <v>4234400</v>
       </c>
       <c r="I61" s="3">
-        <v>3340200</v>
+        <v>4178700</v>
       </c>
       <c r="J61" s="3">
+        <v>4111800</v>
+      </c>
+      <c r="K61" s="3">
         <v>3338800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4148000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4177300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4175400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3475700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3503500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1282500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1757600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1840400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1920900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2109200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1374800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1356700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>446600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>439600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>582700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1062800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1116400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1145800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>745700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>727000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>674400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>624800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>355000</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1125300</v>
+        <v>182000</v>
       </c>
       <c r="E62" s="3">
-        <v>941600</v>
+        <v>143800</v>
       </c>
       <c r="F62" s="3">
-        <v>947600</v>
+        <v>87400</v>
       </c>
       <c r="G62" s="3">
-        <v>976500</v>
+        <v>74500</v>
       </c>
       <c r="H62" s="3">
-        <v>1064600</v>
+        <v>80300</v>
       </c>
       <c r="I62" s="3">
-        <v>1051800</v>
+        <v>82600</v>
       </c>
       <c r="J62" s="3">
+        <v>85100</v>
+      </c>
+      <c r="K62" s="3">
         <v>917500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1126800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1115800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1013800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>679500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>813800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>758000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>647000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>559000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>494400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>615700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>462400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>332500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>324100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>418800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>400200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>182800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>161300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>200200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>177900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>148500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>208100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>179600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>157100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>142600</v>
       </c>
-      <c r="AI62" s="3" t="s">
+      <c r="AJ62" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12702700</v>
+        <v>13663100</v>
       </c>
       <c r="E66" s="3">
-        <v>12428000</v>
+        <v>12603700</v>
       </c>
       <c r="F66" s="3">
-        <v>12289400</v>
+        <v>12326100</v>
       </c>
       <c r="G66" s="3">
-        <v>11557800</v>
+        <v>12185600</v>
       </c>
       <c r="H66" s="3">
-        <v>11140800</v>
+        <v>11447100</v>
       </c>
       <c r="I66" s="3">
-        <v>11150600</v>
+        <v>11032100</v>
       </c>
       <c r="J66" s="3">
+        <v>11052300</v>
+      </c>
+      <c r="K66" s="3">
         <v>11287100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12385100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12094500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12073400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11357300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10761500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7962900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7518900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7072800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6219300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5750500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4312200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4061700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2829400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2585700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2397500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2435800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2227300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2126800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1681400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1519300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1340700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1138200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>800200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>406400</v>
       </c>
-      <c r="AI66" s="3" t="s">
+      <c r="AJ66" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6436,7 +6604,7 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
-        <v>205100</v>
+        <v>0</v>
       </c>
       <c r="AF70" s="3">
         <v>205100</v>
@@ -6448,10 +6616,13 @@
         <v>205100</v>
       </c>
       <c r="AI70" s="3">
+        <v>205100</v>
+      </c>
+      <c r="AJ70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8375300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8524100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8606000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8582300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8472600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8323400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8645000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8733100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-9159800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8594600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7661400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7195400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6577700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6004700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5571300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5148600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4625000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4205000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3812100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3530500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3246800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3039200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2758100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2067700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1791100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1572800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1322100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1106500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-843800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-670100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-578000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-505000</v>
       </c>
-      <c r="AI72" s="3" t="s">
+      <c r="AJ72" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7916400</v>
+      </c>
+      <c r="E76" s="3">
         <v>6867300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6667100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6593800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6467300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6511500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6093300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5715700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4897200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5373200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6261200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7398700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7787300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3560200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3403700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3382900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>741200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>853800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>920600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1162400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1252500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1433400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1529500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-243100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>25100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>228600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>289100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>469000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-424600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-279000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-192800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-125700</v>
       </c>
-      <c r="AI76" s="3" t="s">
+      <c r="AJ76" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>81900</v>
+        <v>153300</v>
       </c>
       <c r="E81" s="3">
+        <v>79900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-23700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-109700</v>
       </c>
-      <c r="G81" s="3">
-        <v>-149200</v>
-      </c>
       <c r="H81" s="3">
-        <v>321600</v>
+        <v>-144000</v>
       </c>
       <c r="I81" s="3">
+        <v>331000</v>
+      </c>
+      <c r="J81" s="3">
         <v>88100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>426800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-565300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-933100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-579800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-617600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-573000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-433400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-422700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-523600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-420000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-393000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-281500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-283800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-207600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-281100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-690400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-276600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-218300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-250700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-215600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-262700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-132700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-92100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-73100</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>-120200</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>120200</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+        <v>404900</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>-89700</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>89700</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7451,21 +7650,21 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>11</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V83" s="3">
         <v>38200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>34600</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>11</v>
       </c>
@@ -7478,32 +7677,35 @@
       <c r="AA83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>11</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG83" s="3">
         <v>9000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8800</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AI83" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1170100</v>
+      </c>
+      <c r="E89" s="3">
         <v>617900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>468500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>278800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>599800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>595500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>605500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>319700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-166300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-485500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-723700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-304800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>62700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>132400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>318300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>185400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>296000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>298100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-223700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-27800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>380800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-265300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-324400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>112300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-188800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-94400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-38200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-89800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-65400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-65800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-42100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-36500</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8365,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-807200</v>
+        <v>90800</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-64000</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-64600</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-44000</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-32000</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-101000</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8195,21 +8416,21 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>11</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V91" s="3">
         <v>-50100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-42400</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>11</v>
       </c>
@@ -8222,32 +8443,35 @@
       <c r="AA91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>11</v>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1716100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-709900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-853800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1048600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-888300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3193900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-673800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>51500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-402100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-947500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1130700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1775500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-341900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1145500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-504300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-667400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>91300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-163700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-147100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-143700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-157700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>29400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-91300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-157100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-40000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-51100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-50100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>12900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-13400</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>557800</v>
+      </c>
+      <c r="E100" s="3">
         <v>242600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>183800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>183400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>124500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>59200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-513700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>474000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>297600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>142400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>386000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6835200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>138800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>41600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2198600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>747700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>811600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-24800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1045000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>989800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-983100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1527900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-149800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>151700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>545300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>927400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>69500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>270000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>357000</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-44800</v>
+        <v>-54200</v>
       </c>
       <c r="E101" s="3">
-        <v>-72800</v>
+        <v>-71600</v>
       </c>
       <c r="F101" s="3">
-        <v>68300</v>
+        <v>49500</v>
       </c>
       <c r="G101" s="3">
-        <v>-54200</v>
+        <v>109100</v>
       </c>
       <c r="H101" s="3">
-        <v>-71600</v>
+        <v>-124900</v>
       </c>
       <c r="I101" s="3">
-        <v>49500</v>
+        <v>-119700</v>
       </c>
       <c r="J101" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="K101" s="3">
         <v>109100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-124900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-119700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>6500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-33000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>14500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-46300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>59000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>13000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>60500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-51800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>23200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>12900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>15300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-17300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>191100</v>
+      </c>
+      <c r="E102" s="3">
         <v>105700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-274300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-518000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-218100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2671100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-33400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-219200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1255100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1687800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6523100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-859700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-190800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2068300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>855400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1006400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-447300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>896700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1225800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1231900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1420700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-648000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>273600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>299300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-110600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>842800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-69600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>194300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>286700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-31900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-18000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>SE</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4950400</v>
+      </c>
+      <c r="E8" s="3">
         <v>4328200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3806900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3734300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3616600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3310200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3095700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3041100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3451600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3156000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2942600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2899600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3222100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2688900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2280500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1763600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1566600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1212200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>882000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>714900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>777200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>610100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>436200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>351900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>283200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>204900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>183800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>155000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>124600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>94100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>101500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>93900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>88500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2745000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2467200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2222100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2180600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2091800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1868900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1644800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1624400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1754300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1928200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1852400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1729500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1911400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1680200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1349700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1118200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1032800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>804600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>681200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>508100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>512400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>407000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>338700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>312400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>291200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>199300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>175200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>146500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>101100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>83300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>75700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>66800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>63200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2205500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1861100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1584800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1553800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1524800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1441300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1450900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1416700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1697300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1227800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1090200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1170100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1310700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1008700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>930800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>645400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>533800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>407600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>200800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>206800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>264800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>203100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>97500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>39500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>23500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>10800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>25800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>27100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>301200</v>
+      </c>
+      <c r="E12" s="3">
         <v>302000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>298500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>304400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>279800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>280500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>283300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>320500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>244200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>421000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>370900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>340400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>286600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>231400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>172600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>141100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>109500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>104300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>75300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>63900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>48800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>43600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>35100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>28500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>26600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>17300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>8700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,44 +1377,47 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>11</v>
+      <c r="D14" s="3">
+        <v>52500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3">
         <v>84100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>41700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="3">
         <v>145600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-22000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>177300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1414,8 +1433,8 @@
       <c r="S14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1465,34 +1484,37 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E15" s="3">
         <v>110200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>102300</v>
       </c>
       <c r="F15" s="3">
         <v>102300</v>
       </c>
       <c r="G15" s="3">
+        <v>102300</v>
+      </c>
+      <c r="H15" s="3">
         <v>101500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>107100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>120200</v>
       </c>
       <c r="J15" s="3">
         <v>120200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>120200</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1506,8 +1528,8 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>11</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>11</v>
@@ -1524,15 +1546,15 @@
       <c r="U15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="W15" s="3">
         <v>11000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>10100</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1557,20 +1579,23 @@
       <c r="AF15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH15" s="3">
         <v>2100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>2000</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4644700</v>
+      </c>
+      <c r="E17" s="3">
         <v>4125800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3724000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3663200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3673100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3437900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2811800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2798000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2909000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3651600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3779300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3397600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3664200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3147400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2614600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2112100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1923900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1517600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1254800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>982600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1007300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>797600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>670700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>591100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>608200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>451100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>403300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>353100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>315700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>254800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>184000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>162000</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK17" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>305800</v>
+      </c>
+      <c r="E18" s="3">
         <v>202400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>82900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>71100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-56500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-127700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>283800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>243100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>542600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-495600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-836700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-498000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-442100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-458500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-334100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-348500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-357300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-305400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-372800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-267700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-230100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-187500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-234500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-239200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-325000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-246200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-219500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-198100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-191100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-160700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-82500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-68100</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK18" s="3">
         <v>-52900</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-43500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-57600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>17300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-45400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-109400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-153900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-21400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-18700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>24200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-89600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-28900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>51000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>35900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>20600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-19100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-432700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>62900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>40800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-27800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-53200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>34300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-200</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>390700</v>
+      </c>
+      <c r="E21" s="3">
         <v>356100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>242800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>164800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>27700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>24800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>513400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>356600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>384000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-476300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-844500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-402800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-258200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-420100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-331200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-287800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V21" s="3">
         <v>-318400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-193600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-193500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-108900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-250100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-646400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-287600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-171100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-244000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-193200</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-73900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-59400</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>11</v>
+      <c r="D22" s="3">
+        <v>9300</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="3">
         <v>9700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="3">
         <v>10400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>52300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>37000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>22700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>26900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>34900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>45400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>43300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>24600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>17200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10100</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>9900</v>
       </c>
       <c r="AB22" s="3">
         <v>9900</v>
       </c>
       <c r="AC22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AD22" s="3">
         <v>3000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2300</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>326800</v>
+      </c>
+      <c r="E23" s="3">
         <v>245900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>140500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>55800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-34700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-82300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>393200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>149200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>377800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-504800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-869500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-504100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-513100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-471400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-359100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-371700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-481800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-379800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-365200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-256500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-245200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-177700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-263700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-682000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-272000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-215300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-250300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-216300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-253400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-134900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-89700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-70500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-68000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-56800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>89200</v>
+      </c>
+      <c r="E24" s="3">
         <v>92600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>60600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>76900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>62200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>61900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-43500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>65300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>64800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>81800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>105600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>101000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>75200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>51000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>44200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>46400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>27800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>23200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>36000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>27400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>15300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>8700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>237600</v>
+      </c>
+      <c r="E26" s="3">
         <v>153300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>79900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-111600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-144000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>331000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>87300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>421300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-570100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-934200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-585900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-618700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-572400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-434300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-422700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-526000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-426200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-393000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-279700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-281200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-205000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-279000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-689200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-275000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-217300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-250100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-215600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-262200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-132800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-91900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-72400</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ26" s="3">
+      <c r="AJ26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-60300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>237300</v>
+      </c>
+      <c r="E27" s="3">
         <v>153300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>79900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-109700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-144000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>331000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>88100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>426800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-565300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-933100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-579800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-617600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-573000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-433400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-422700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-523600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-420000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-393000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-281500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-283800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-207600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-281100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-690400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-276600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-218300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-250700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-215600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-262700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-132700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-92100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-73100</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ27" s="3">
+      <c r="AJ27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E32" s="3">
         <v>43500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>57600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-17300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>45400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>109400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>153900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>21400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>18700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>89600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>28900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-51000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-35900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-20600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>19100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>432700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-62900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>27800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>9600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>53200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-34300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>200</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>237300</v>
+      </c>
+      <c r="E33" s="3">
         <v>153300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>79900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-109700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-144000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>331000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>88100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>426800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-565300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-933100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-579800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-617600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-573000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-433400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-422700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-523600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-420000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-393000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-281500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-283800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-207600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-281100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-690400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-276600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-218300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-250700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-215600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-262700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-132700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-92100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-73100</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ33" s="3">
+      <c r="AJ33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>237300</v>
+      </c>
+      <c r="E35" s="3">
         <v>153300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>79900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-109700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-144000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>331000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>88100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>426800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-565300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-933100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-579800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-617600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-573000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-433400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-422700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-523600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-420000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-393000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-281500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-283800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-207600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-281100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-690400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-276600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-218300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-250700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-215600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-262700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-132700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-92100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-73100</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ35" s="3">
+      <c r="AJ35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,190 +3784,194 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2405200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2538700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2646500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2460800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2811100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3219900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3524400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6082700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6029900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6253400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6493200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7683700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9247800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11126200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4645400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5752600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6166900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3509000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3432800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2599700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3119000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2297200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2308100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2362500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1002800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1209200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1477100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1172400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1347400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>581500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>651100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>456800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>170100</v>
       </c>
-      <c r="AJ41" s="3" t="s">
+      <c r="AK41" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6215400</v>
+      </c>
+      <c r="E42" s="3">
         <v>5374500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3387500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2941000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2547600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2762700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2174900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>506400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>864300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1042300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1287500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1116900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>911300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>706000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>962100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>309700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>126100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>42300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>14700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>30500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>102300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>9400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>8900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>700</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
@@ -3890,233 +3979,242 @@
         <v>0</v>
       </c>
       <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
         <v>18000</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AI42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="3" t="s">
+      <c r="AI42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4777300</v>
+      </c>
+      <c r="E43" s="3">
         <v>4227800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3464200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3280500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4538700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2313000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2198800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2246600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2336000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2386500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2295000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2124600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1905400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1433700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1159100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>795400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>668400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>295900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>254600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>163600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>191800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>140500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>152700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>151500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>103000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>66500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>61000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>73100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>64100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>59200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>47900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>43200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>37800</v>
       </c>
-      <c r="AJ43" s="3" t="s">
+      <c r="AK43" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E44" s="3">
         <v>200700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>157500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>142300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>125400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>116300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>98500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>107300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>109700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>122400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>127200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>139700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>117500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>128700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>99500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>92700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>64200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>61700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>61200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>34200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>26900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>21400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>22500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>25900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>37700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>19600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>16900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>13400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>9800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>7300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ44" s="3" t="s">
+      <c r="AK44" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4129,514 +4227,529 @@
       <c r="F45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="3">
         <v>228800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L45" s="3">
         <v>3348200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2773300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2769200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2765100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2953500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2609100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2530900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2075600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1913400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1654200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1487700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1222600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>970100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>849300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>757500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>652000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>566500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>513100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>424200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>383400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>281500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>218800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>163600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>122800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>98100</v>
       </c>
-      <c r="AJ45" s="3" t="s">
+      <c r="AK45" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16857700</v>
+      </c>
+      <c r="E46" s="3">
         <v>15554200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12880700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12381300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11773900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11973900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11475800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12440300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12688000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12577900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12972100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13829900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15135400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16003700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9397100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9025900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8939000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5563100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5251000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4050600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4410100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3317800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3249700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3192500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1710700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1808500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1979300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1642300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1720700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>866800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>868200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>628600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>309900</v>
       </c>
-      <c r="AJ46" s="3" t="s">
+      <c r="AK46" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2694300</v>
+      </c>
+      <c r="E47" s="3">
         <v>2974600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3769500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4024600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4262600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3162700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3183300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1789200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1275300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1372000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1383900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1455900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1081800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>370600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>331900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>353500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>307600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>219100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>195200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>143200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>113800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>99100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>100400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>107100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>111000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>118200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>71000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>58500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>28200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>27100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>45100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>45400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>45100</v>
       </c>
-      <c r="AJ47" s="3" t="s">
+      <c r="AK47" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2152500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2327700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2188700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2058500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2223700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2243800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2308400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2372400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2345700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2457200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2214700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2101500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1679600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1353300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>830200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>628600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>621000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>573400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>523500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>486900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>501600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>463100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>425900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>406300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>192400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>147400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>121900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>93900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>74300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>47900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>34100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>32400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>31100</v>
       </c>
-      <c r="AJ48" s="3" t="s">
+      <c r="AK48" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E49" s="3">
         <v>144600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>142100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>152900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>163600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>173400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>176300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>182300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>295200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>482100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>462300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>624000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>592100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>525400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>518500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>509300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>256100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>244000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>260500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>263300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>46000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>45900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>43800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>44900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>43800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>56600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>60500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>64600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>68300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>73000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>24300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>27200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ49" s="3" t="s">
+      <c r="AK49" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>160100</v>
+      </c>
+      <c r="E52" s="3">
         <v>146000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>136000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>127200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>97900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>140400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>164600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>160600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>398600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>393200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>434700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>323400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>267000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>295700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>445400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>405300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>332000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>360900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>374100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>288900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>152700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>156000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>199200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>176100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>134700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>121800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>122600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>111100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>96700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>106400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>92500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>78900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>69700</v>
       </c>
-      <c r="AJ52" s="3" t="s">
+      <c r="AK52" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22625500</v>
+      </c>
+      <c r="E54" s="3">
         <v>21691700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19570000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19095000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18883200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18025100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17652300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17243900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17002800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17282300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17467700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18334600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18756000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18548700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11523000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10922600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10455700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6960600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6604300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5232800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5224200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4081900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4019100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3927000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2192700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2252400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2355400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1970500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1988300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1121200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1064200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>812400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>485800</v>
       </c>
-      <c r="AJ54" s="3" t="s">
+      <c r="AK54" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,162 +5360,166 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>350000</v>
+      </c>
+      <c r="E57" s="3">
         <v>274800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>293700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>280000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>406000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>267900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>219000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>212300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>258600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>289800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>239000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>287100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>213600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>232700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>179600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>152900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>121600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>118400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>96700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>51000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>69400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>48100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>32400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>38100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>37200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>25200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>33900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ57" s="3" t="s">
+      <c r="AK57" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1578900</v>
+      </c>
+      <c r="E58" s="3">
         <v>610300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>518400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>529700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>592900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>380200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>382800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>406100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1436000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>80200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>100000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>11</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5395,34 +5528,34 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>2400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>30700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>24000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>25800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>900</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>2000</v>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AF58" s="3">
         <v>2000</v>
@@ -5434,429 +5567,444 @@
         <v>2000</v>
       </c>
       <c r="AI58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ58" s="3" t="s">
+      <c r="AK58" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6986900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6556000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6000900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5861600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5536800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4785700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4564500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4760800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5241000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6681300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6500800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6567000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6862900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6188300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5704000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4924700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4514400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3654100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2890200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2375300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2262300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1979600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1663600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1371000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1148500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>921400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>744000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>738400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>627000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>438500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>323700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>276700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>255900</v>
       </c>
-      <c r="AJ59" s="3" t="s">
+      <c r="AK59" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11296200</v>
+      </c>
+      <c r="E60" s="3">
         <v>9589400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8617200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8487200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8168900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7030800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6575700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6660200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6935700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7051400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6739800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6854100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7176400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6421000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5883600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5077600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4636100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3772500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2986900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2428600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2362400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2051700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1721800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1410100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1186500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>946500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>777900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>752300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>637700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>449800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>333800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>288100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>263800</v>
       </c>
-      <c r="AJ60" s="3" t="s">
+      <c r="AK60" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2531800</v>
+      </c>
+      <c r="E61" s="3">
         <v>3793400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3724200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3629300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3869500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4234400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4178700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4111800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3338800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4148000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4177300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4175400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3475700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3503500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1282500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1757600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1840400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1920900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2109200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1374800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1356700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>446600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>439600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>582700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1062800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1116400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1145800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>745700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>727000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>674400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>624800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>355000</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>209700</v>
+      </c>
+      <c r="E62" s="3">
         <v>182000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>143800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>87400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>74500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>80300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>82600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>85100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>917500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1126800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1115800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1013800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>679500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>813800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>758000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>647000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>559000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>494400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>615700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>462400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>332500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>324100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>418800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>400200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>182800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>161300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>200200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>177900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>148500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>208100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>179600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>157100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>142600</v>
       </c>
-      <c r="AJ62" s="3" t="s">
+      <c r="AK62" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14147900</v>
+      </c>
+      <c r="E66" s="3">
         <v>13663100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12603700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12326100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12185600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11447100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11032100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11052300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11287100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12385100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12094500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12073400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11357300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10761500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7962900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7518900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7072800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6219300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5750500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4312200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4061700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2829400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2585700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2397500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2435800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2227300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2126800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1681400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1519300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1340700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1138200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>800200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>406400</v>
       </c>
-      <c r="AJ66" s="3" t="s">
+      <c r="AK66" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6607,7 +6774,7 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
-        <v>205100</v>
+        <v>0</v>
       </c>
       <c r="AG70" s="3">
         <v>205100</v>
@@ -6619,10 +6786,13 @@
         <v>205100</v>
       </c>
       <c r="AJ70" s="3">
+        <v>205100</v>
+      </c>
+      <c r="AK70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8138000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8375300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8524100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8606000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8582300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8472600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8323400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8645000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8733100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-9159800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8594600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7661400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7195400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6577700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6004700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5571300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5148600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4625000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-4205000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3812100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3530500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3246800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3039200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2758100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2067700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1791100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1572800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1322100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1106500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-843800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-670100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-578000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-505000</v>
       </c>
-      <c r="AJ72" s="3" t="s">
+      <c r="AK72" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8372300</v>
+      </c>
+      <c r="E76" s="3">
         <v>7916400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6867300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6667100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6593800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6467300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6511500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6093300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5715700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4897200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5373200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6261200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7398700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7787300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3560200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3403700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3382900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>741200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>853800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>920600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1162400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1252500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1433400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1529500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-243100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>25100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>228600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>289100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>469000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-424600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-279000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-192800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-125700</v>
       </c>
-      <c r="AJ76" s="3" t="s">
+      <c r="AK76" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>237300</v>
+      </c>
+      <c r="E81" s="3">
         <v>153300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>79900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-109700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-144000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>331000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>88100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>426800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-565300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-933100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-579800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-617600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-573000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-433400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-422700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-523600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-420000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-393000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-281500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-283800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-207600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-281100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-690400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-276600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-218300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-250700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-215600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-262700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-132700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-92100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-73100</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ81" s="3">
+      <c r="AJ81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,35 +7797,36 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>412200</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="3">
         <v>-120200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>120200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>404900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J83" s="3">
         <v>-89700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>89700</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -7653,21 +7851,21 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>11</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="W83" s="3">
         <v>38200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>34600</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>11</v>
       </c>
@@ -7680,32 +7878,35 @@
       <c r="AB83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>11</v>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH83" s="3">
         <v>9000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>8800</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ83" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1170100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>617900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>468500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>278800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>599800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>595500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>605500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>319700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-166300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-485500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-723700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-304800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>62700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>132400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>318300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>185400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>296000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>298100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-223700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-27800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>380800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-265300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-324400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>112300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-188800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-94400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-38200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-89800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-65400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-65800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-42100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-36500</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,35 +8585,36 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="E91" s="3">
         <v>90800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-64000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-64600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-44000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-32000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-101000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -8419,21 +8639,21 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>11</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="W91" s="3">
         <v>-50100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-42400</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>11</v>
       </c>
@@ -8446,32 +8666,35 @@
       <c r="AB91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>11</v>
+      <c r="AE91" s="3">
+        <v>0</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AJ91" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1761100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1716100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-709900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-853800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1048600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-888300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3193900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-673800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>51500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-402100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-947500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1130700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1775500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-341900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1145500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-504300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-667400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>91300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-163700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-147100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-143700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-157700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>29400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-91300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-157100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-40000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-51100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-50100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-13400</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700200</v>
+      </c>
+      <c r="E100" s="3">
         <v>557800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>242600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>183800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>183400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>124500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>59200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-513700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>474000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>297600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>142400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>386000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6835200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>138800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>41600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2198600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>747700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>811600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-24800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1045000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>989800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-983100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1527900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-149800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>151700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>545300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>927400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>69500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>270000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>357000</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-54200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-71600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>49500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>109100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-124900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-119700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>109100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-124900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-119700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>6500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>14500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-46300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>59000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>13000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>60500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-51800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>23200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>12900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-12900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>15300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-17300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-184700</v>
+      </c>
+      <c r="E102" s="3">
         <v>191100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>105700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-274300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-518000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-218100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2671100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-33400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-219200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1255100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1687800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6523100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-859700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-190800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2068300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>855400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1006400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-447300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>896700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1225800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1231900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1420700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-648000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>273600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>299300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-110600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>842800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-69600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>194300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>286700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-31900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-18000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>SE</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4841100</v>
+      </c>
+      <c r="E8" s="3">
         <v>4950400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4328200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3806900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3734300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3616600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3310200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3095700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3041100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3451600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3156000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2942600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2899600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3222100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2688900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2280500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1763600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1566600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1212200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>882000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>714900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>777200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>610100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>436200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>351900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>283200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>204900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>183800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>155000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>124600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>94100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>101500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>93900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>88500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2604900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2745000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2467200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2222100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2180600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2091800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1868900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1644800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1624400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1754300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1928200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1852400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1729500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1911400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1680200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1349700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1118200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1032800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>804600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>681200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>508100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>512400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>407000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>338700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>312400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>291200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>199300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>175200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>146500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>101100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>83300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>75700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>66800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>63200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2236200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2205500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1861100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1584800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1553800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1524800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1441300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1450900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1416700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1697300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1227800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1090200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1170100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1310700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1008700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>930800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>645400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>533800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>407600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>200800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>206800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>264800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>203100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>97500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>39500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>23500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>10800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>25800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>27100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>25300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,115 +1179,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>295900</v>
+      </c>
+      <c r="E12" s="3">
         <v>301200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>302000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>298500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>304400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>279800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>280500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>283300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>320500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>244200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>421000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>370900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>340400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>286600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>231400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>172600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>141100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>109500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>104300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>75300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>63900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>48800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>43600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>35100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>28500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>26600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>17300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>12900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>10700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,47 +1397,50 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E14" s="3">
         <v>52500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="3">
         <v>84100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>41700</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" s="3">
         <v>145600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-22000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>177300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1436,8 +1456,8 @@
       <c r="T14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1487,37 +1507,40 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E15" s="3">
         <v>96200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>110200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>102300</v>
       </c>
       <c r="G15" s="3">
         <v>102300</v>
       </c>
       <c r="H15" s="3">
+        <v>102300</v>
+      </c>
+      <c r="I15" s="3">
         <v>101500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>107100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>120200</v>
       </c>
       <c r="K15" s="3">
         <v>120200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>120200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1531,8 +1554,8 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>11</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>11</v>
@@ -1549,15 +1572,15 @@
       <c r="V15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="X15" s="3">
         <v>11000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10100</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1582,20 +1605,23 @@
       <c r="AG15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI15" s="3">
         <v>2100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AK15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4384700</v>
+      </c>
+      <c r="E17" s="3">
         <v>4644700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4125800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3724000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3663200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3673100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3437900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2811800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2798000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2909000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3651600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3779300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3397600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3664200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3147400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2614600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2112100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1923900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1517600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1254800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>982600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1007300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>797600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>670700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>591100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>608200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>451100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>403300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>353100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>315700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>254800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>184000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>162000</v>
       </c>
-      <c r="AJ17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL17" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>456400</v>
+      </c>
+      <c r="E18" s="3">
         <v>305800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>202400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>82900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>71100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-56500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-127700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>283800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>243100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>542600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-495600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-836700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-498000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-442100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-458500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-334100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-348500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-357300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-305400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-372800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-267700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-230100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-187500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-234500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-239200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-325000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-246200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-219500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-198100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-191100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-160700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-82500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-68100</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL18" s="3">
         <v>-52900</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1916,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>11200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-43500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-57600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>17300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-45400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-109400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-153900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-21400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>24200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-89600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-28900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>51000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>35900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-19100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-432700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>62900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>40800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-27800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-53200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>34300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>546200</v>
+      </c>
+      <c r="E21" s="3">
         <v>390700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>356100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>242800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>164800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>513400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>356600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>384000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-476300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-844500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-402800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-258200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-420100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-331200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-287800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="W21" s="3">
         <v>-318400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-193600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-193500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-108900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-250100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-646400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-287600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-171100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-244000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-193200</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-73900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-59400</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AK21" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E22" s="3">
         <v>9300</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="3">
         <v>9700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="3">
         <v>10400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>52300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>37000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>22700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>26900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>34900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>45400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>43300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>17200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10100</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>9900</v>
       </c>
       <c r="AC22" s="3">
         <v>9900</v>
       </c>
       <c r="AD22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AE22" s="3">
         <v>3000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>6700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
-      </c>
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>547100</v>
+      </c>
+      <c r="E23" s="3">
         <v>326800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>245900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>140500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>55800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-34700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-82300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>393200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>149200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>377800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-504800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-869500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-504100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-513100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-471400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-359100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-371700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-481800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-379800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-365200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-256500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-245200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-177700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-263700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-682000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-272000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-215300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-250300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-216300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-253400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-134900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-89700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-70500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-68000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-56800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>136300</v>
+      </c>
+      <c r="E24" s="3">
         <v>89200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>92600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>60600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>78800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>76900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>61700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>62200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>61900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-43500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>65300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>64800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>81800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>105600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>101000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>75200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>51000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>44200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>46400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>27800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>23200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>36000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>27400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>15300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>8700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>410800</v>
+      </c>
+      <c r="E26" s="3">
         <v>237600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>153300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>79900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-111600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-144000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>331000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>87300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>421300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-570100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-934200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-585900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-618700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-572400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-434300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-422700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-526000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-426200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-393000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-279700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-281200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-205000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-279000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-689200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-275000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-217300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-250100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-215600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-262200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-132800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-91900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-72400</v>
       </c>
-      <c r="AJ26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL26" s="3">
         <v>-60300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>403100</v>
+      </c>
+      <c r="E27" s="3">
         <v>237300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>153300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>79900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-109700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-144000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>331000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>88100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>426800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-565300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-933100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-579800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-617600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-573000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-433400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-422700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-523600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-420000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-393000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-281500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-283800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-207600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-281100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-690400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-276600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-218300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-250700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-215600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-262700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-132700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-92100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-73100</v>
       </c>
-      <c r="AJ27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL27" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>43500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>57600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-17300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>45400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>109400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>153900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>21400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>18700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-24200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>89600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>28900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-51000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-35900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>19100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>432700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-62900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>27800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>9600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>53200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-34300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>200</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>403100</v>
+      </c>
+      <c r="E33" s="3">
         <v>237300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>153300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>79900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-109700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-144000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>331000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>88100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>426800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-565300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-933100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-579800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-617600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-573000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-433400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-422700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-523600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-420000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-393000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-281500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-283800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-207600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-281100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-690400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-276600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-218300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-250700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-215600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-262700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-132700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-92100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-73100</v>
       </c>
-      <c r="AJ33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL33" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>403100</v>
+      </c>
+      <c r="E35" s="3">
         <v>237300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>153300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>79900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-109700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-144000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>331000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>88100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>426800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-565300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-933100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-579800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-617600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-573000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-433400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-422700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-523600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-420000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-393000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-281500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-283800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-207600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-281100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-690400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-276600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-218300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-250700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-215600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-262700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-132700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-92100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-73100</v>
       </c>
-      <c r="AJ35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL35" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,196 +3871,200 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2183000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2405200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2538700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2646500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2460800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2811100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3219900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3524400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6082700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6029900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6253400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6493200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7683700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9247800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11126200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4645400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5752600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6166900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3509000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3432800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2599700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3119000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2297200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2308100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2362500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1002800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1209200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1477100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1172400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1347400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>581500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>651100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>456800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>170100</v>
       </c>
-      <c r="AK41" s="3" t="s">
+      <c r="AL41" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6243200</v>
+      </c>
+      <c r="E42" s="3">
         <v>6215400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5374500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3387500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2941000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2547600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2762700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2174900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>506400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>864300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1042300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1287500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1116900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>911300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>706000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>962100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>309700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>126100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>42300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>14700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>30500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>102300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>8900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>700</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
       <c r="AD42" s="3">
         <v>0</v>
       </c>
@@ -3982,247 +4072,256 @@
         <v>0</v>
       </c>
       <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
         <v>18000</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AI42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AJ42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="s">
+      <c r="AJ42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4777300</v>
+        <v>5507100</v>
       </c>
       <c r="E43" s="3">
+        <v>6057900</v>
+      </c>
+      <c r="F43" s="3">
         <v>4227800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3464200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3280500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4538700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2313000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2198800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2246600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2336000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2386500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2295000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2124600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1905400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1433700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1159100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>795400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>668400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>295900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>254600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>163600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>191800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>140500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>152700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>151500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>103000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>66500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>61000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>73100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>64100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>59200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>47900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>43200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>37800</v>
       </c>
-      <c r="AK43" s="3" t="s">
+      <c r="AL43" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>172700</v>
+      </c>
+      <c r="E44" s="3">
         <v>143200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>200700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>157500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>142300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>125400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>116300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>98500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>107300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>109700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>122400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>127200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>139700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>117500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>128700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>99500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>92700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>64200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>61700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>61200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>34200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>26900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>21400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>22500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>25900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>37700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>19600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>16900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>13400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>9800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>7300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3900</v>
       </c>
-      <c r="AK44" s="3" t="s">
+      <c r="AL44" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>11</v>
+      <c r="E45" s="3">
+        <v>263200</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -4230,526 +4329,541 @@
       <c r="G45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" s="3">
         <v>228800</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M45" s="3">
         <v>3348200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2773300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2769200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2765100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2953500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2609100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2530900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2075600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1913400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1654200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1487700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1222600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>970100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>849300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>757500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>652000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>566500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>513100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>424200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>383400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>281500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>218800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>163600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>122800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>98100</v>
       </c>
-      <c r="AK45" s="3" t="s">
+      <c r="AL45" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17779300</v>
+      </c>
+      <c r="E46" s="3">
         <v>16857700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15554200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12880700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12381300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11773900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11973900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11475800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12440300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12688000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12577900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12972100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13829900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15135400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16003700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9397100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9025900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8939000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5563100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5251000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4050600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4410100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3317800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3249700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3192500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1710700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1808500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1979300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1642300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1720700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>866800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>868200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>628600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>309900</v>
       </c>
-      <c r="AK46" s="3" t="s">
+      <c r="AL46" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2828500</v>
+      </c>
+      <c r="E47" s="3">
         <v>2694300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2974600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3769500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4024600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4262600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3162700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3183300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1789200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1275300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1372000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1383900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1455900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1081800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>370600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>331900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>353500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>307600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>219100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>195200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>143200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>113800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>99100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>100400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>107100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>111000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>118200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>71000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>58500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>28200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>27100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>45100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>45400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>45100</v>
       </c>
-      <c r="AK47" s="3" t="s">
+      <c r="AL47" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2248300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2152500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2327700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2188700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2058500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2223700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2243800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2308400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2372400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2345700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2457200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2214700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2101500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1679600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1353300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>830200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>628600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>621000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>573400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>523500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>486900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>501600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>463100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>425900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>406300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>192400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>147400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>121900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>93900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>74300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>47900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>34100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>31100</v>
       </c>
-      <c r="AK48" s="3" t="s">
+      <c r="AL48" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E49" s="3">
         <v>134900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>144600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>142100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>152900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>163600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>173400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>176300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>182300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>295200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>482100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>462300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>624000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>592100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>525400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>518500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>509300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>256100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>244000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>260500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>263300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>46000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>45900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>43800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>44900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>43800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>56600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>60500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>64600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>68300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>73000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>24300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>27200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>30000</v>
       </c>
-      <c r="AK49" s="3" t="s">
+      <c r="AL49" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>160100</v>
+        <v>194800</v>
       </c>
       <c r="E52" s="3">
+        <v>139600</v>
+      </c>
+      <c r="F52" s="3">
         <v>146000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>136000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>127200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>97900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>140400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>164600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>160600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>398600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>393200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>434700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>323400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>267000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>295700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>445400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>405300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>332000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>360900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>374100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>288900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>152700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>156000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>199200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>176100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>134700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>121800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>122600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>111100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>96700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>106400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>92500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>78900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>69700</v>
       </c>
-      <c r="AK52" s="3" t="s">
+      <c r="AL52" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23843100</v>
+      </c>
+      <c r="E54" s="3">
         <v>22625500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21691700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19570000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19095000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18883200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18025100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17652300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17243900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17002800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17282300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17467700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18334600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18756000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18548700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11523000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10922600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10455700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6960600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6604300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5232800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5224200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4081900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4019100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3927000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2192700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2252400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2355400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1970500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1988300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1121200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1064200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>812400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>485800</v>
       </c>
-      <c r="AK54" s="3" t="s">
+      <c r="AL54" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,168 +5491,172 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>350000</v>
+        <v>320900</v>
       </c>
       <c r="E57" s="3">
+        <v>604700</v>
+      </c>
+      <c r="F57" s="3">
         <v>274800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>293700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>280000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>406000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>267900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>219000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>212300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>258600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>289800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>239000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>287100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>213600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>232700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>179600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>152900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>121600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>118400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>96700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>51000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>69400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>48100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>32400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>38100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>37200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>25200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>33900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>13900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6000</v>
       </c>
-      <c r="AK57" s="3" t="s">
+      <c r="AL57" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1578900</v>
+        <v>1580600</v>
       </c>
       <c r="E58" s="3">
+        <v>1583400</v>
+      </c>
+      <c r="F58" s="3">
         <v>610300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>518400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>529700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>592900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>380200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>382800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>406100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1436000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>80200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>11</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5531,34 +5665,34 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>2400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>30700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>24000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>25800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>900</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>2000</v>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AG58" s="3">
         <v>2000</v>
@@ -5570,441 +5704,456 @@
         <v>2000</v>
       </c>
       <c r="AJ58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AK58" s="3">
         <v>1900</v>
       </c>
-      <c r="AK58" s="3" t="s">
+      <c r="AL58" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6986900</v>
+        <v>7735900</v>
       </c>
       <c r="E59" s="3">
+        <v>7179300</v>
+      </c>
+      <c r="F59" s="3">
         <v>6556000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6000900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5861600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5536800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4785700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4564500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4760800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5241000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6681300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6500800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6567000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6862900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6188300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5704000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4924700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4514400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3654100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2890200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2375300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2262300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1979600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1663600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1371000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1148500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>921400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>744000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>738400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>627000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>438500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>323700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>276700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>255900</v>
       </c>
-      <c r="AK59" s="3" t="s">
+      <c r="AL59" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11801300</v>
+      </c>
+      <c r="E60" s="3">
         <v>11296200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9589400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8617200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8487200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8168900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7030800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6575700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6660200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6935700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7051400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6739800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6854100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7176400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6421000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5883600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5077600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4636100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3772500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2986900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2428600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2362400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2051700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1721800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1410100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1186500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>946500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>777900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>752300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>637700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>449800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>333800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>288100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>263800</v>
       </c>
-      <c r="AK60" s="3" t="s">
+      <c r="AL60" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2531800</v>
+        <v>2567500</v>
       </c>
       <c r="E61" s="3">
+        <v>2540800</v>
+      </c>
+      <c r="F61" s="3">
         <v>3793400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3724200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3629300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3869500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4234400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4178700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4111800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3338800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4148000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4177300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4175400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3475700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3503500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1282500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1757600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1840400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1920900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2109200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1374800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1356700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>446600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>439600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>582700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1062800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1116400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1145800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>745700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>727000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>674400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>624800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>355000</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>209700</v>
+        <v>209600</v>
       </c>
       <c r="E62" s="3">
+        <v>200700</v>
+      </c>
+      <c r="F62" s="3">
         <v>182000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>143800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>87400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>74500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>80300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>82600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>85100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>917500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1126800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1115800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1013800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>679500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>813800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>758000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>647000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>559000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>494400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>615700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>462400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>332500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>324100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>418800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>400200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>182800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>161300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>200200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>177900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>148500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>208100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>179600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>157100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>142600</v>
       </c>
-      <c r="AK62" s="3" t="s">
+      <c r="AL62" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14768700</v>
+      </c>
+      <c r="E66" s="3">
         <v>14147900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13663100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12603700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12326100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12185600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11447100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11032100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11052300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11287100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12385100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12094500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12073400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11357300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10761500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7962900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7518900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7072800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6219300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5750500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4312200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4061700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2829400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2585700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2397500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2435800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2227300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2126800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1681400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1519300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1340700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1138200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>800200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>406400</v>
       </c>
-      <c r="AK66" s="3" t="s">
+      <c r="AL66" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6777,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="AG70" s="3">
-        <v>205100</v>
+        <v>0</v>
       </c>
       <c r="AH70" s="3">
         <v>205100</v>
@@ -6789,10 +6957,13 @@
         <v>205100</v>
       </c>
       <c r="AK70" s="3">
+        <v>205100</v>
+      </c>
+      <c r="AL70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7735000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8138000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8375300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8524100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8606000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8582300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8472600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8323400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8645000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8733100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-9159800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8594600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7661400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7195400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6577700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6004700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5571300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5148600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-4625000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4205000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3812100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3530500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3246800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3039200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2758100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2067700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1791100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1572800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1322100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1106500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-843800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-670100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-578000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-505000</v>
       </c>
-      <c r="AK72" s="3" t="s">
+      <c r="AL72" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8963400</v>
+      </c>
+      <c r="E76" s="3">
         <v>8372300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7916400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6867300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6667100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6593800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6467300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6511500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6093300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5715700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4897200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5373200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6261200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7398700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7787300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3560200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3403700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3382900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>741200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>853800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>920600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1162400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1252500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1433400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1529500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-243100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>25100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>228600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>289100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>469000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-424600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-279000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-192800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-125700</v>
       </c>
-      <c r="AK76" s="3" t="s">
+      <c r="AL76" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>403100</v>
+      </c>
+      <c r="E81" s="3">
         <v>237300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>153300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>79900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-109700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-144000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>331000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>88100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>426800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-565300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-933100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-579800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-617600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-573000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-433400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-422700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-523600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-420000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-393000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-281500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-283800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-207600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-281100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-690400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-276600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-218300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-250700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-215600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-262700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-132700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-92100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-73100</v>
       </c>
-      <c r="AJ81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL81" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,38 +7996,39 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E83" s="3">
         <v>412200</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="3">
         <v>-120200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>120200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>404900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K83" s="3">
         <v>-89700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>89700</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -7854,21 +8053,21 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>11</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="X83" s="3">
         <v>38200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>34600</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>11</v>
       </c>
@@ -7881,32 +8080,35 @@
       <c r="AC83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
+      <c r="AD83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>11</v>
+      <c r="AF83" s="3">
+        <v>0</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI83" s="3">
         <v>9000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AK83" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>756900</v>
+      </c>
+      <c r="E89" s="3">
         <v>1021000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1170100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>617900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>468500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>278800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>599800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>595500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>605500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>319700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-166300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-485500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-723700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-304800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>62700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>132400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>318300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>185400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>296000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>298100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-223700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-27800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>380800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-265300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-17800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-324400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>112300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-188800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-94400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-38200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-89800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-65400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-65800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-42100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-36500</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,38 +8806,39 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-89000</v>
+      <c r="D91" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E91" s="3">
+        <v>-317900</v>
+      </c>
+      <c r="F91" s="3">
         <v>90800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-64000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-64600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-44000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-101000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -8642,21 +8863,21 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>11</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="X91" s="3">
         <v>-50100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-42400</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>11</v>
       </c>
@@ -8669,32 +8890,35 @@
       <c r="AC91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>11</v>
+      <c r="AF91" s="3">
+        <v>0</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AK91" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1114700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1761100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1716100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-709900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-853800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1048600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-888300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3193900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-673800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>51500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-402100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-947500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1130700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1775500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-341900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1145500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-504300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-667400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>91300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-163700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-147100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-143700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-157700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>29400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-91300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-157100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-51100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-50100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>12900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-13400</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>274400</v>
+      </c>
+      <c r="E100" s="3">
         <v>700200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>557800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>242600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>183800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>183400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>124500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>59200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-513700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>474000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>297600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>142400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>386000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6835200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>138800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>41600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2198600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>747700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>811600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-24800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1045000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>989800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-983100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1527900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-149800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>151700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>545300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>927400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>69500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>270000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>357000</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E101" s="3">
         <v>68300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-54200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-71600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>49500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>109100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-124900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-119700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>109100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-124900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-119700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-33000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>14500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-46300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>59000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>13000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>60500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-51800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>23200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>12900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>15300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-17300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-65600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-184700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>191100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>105700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-274300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-518000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-218100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2671100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-33400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-219200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1255100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1687800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6523100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-859700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-190800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2068300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>855400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1006400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-447300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>896700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1225800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1231900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1420700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-648000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>273600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>299300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-110600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>842800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-69600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>194300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>286700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-31900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-18000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>SE</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>4841100</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3">
         <v>4950400</v>
       </c>
-      <c r="F8" s="3">
-        <v>4328200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3806900</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3734300</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="3">
         <v>3616600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3310200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3095700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3041100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3451600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3156000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2942600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2899600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3222100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2688900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2280500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1763600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1566600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1212200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>882000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>714900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>777200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>610100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>436200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>351900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>283200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>204900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>183800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>155000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>124600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>94100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>101500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>93900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>88500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>2604900</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3">
         <v>2745000</v>
       </c>
-      <c r="F9" s="3">
-        <v>2467200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2222100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2180600</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="3">
         <v>2091800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1868900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1644800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1624400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1754300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1928200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1852400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1729500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1911400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1680200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1349700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1118200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1032800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>804600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>681200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>508100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>512400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>407000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>338700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>312400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>291200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>199300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>175200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>146500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>101100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>83300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>75700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>66800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>63200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>2236200</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3">
         <v>2205500</v>
       </c>
-      <c r="F10" s="3">
-        <v>1861100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1584800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1553800</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="3">
         <v>1524800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1441300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1450900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1416700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1697300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1227800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1090200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1170100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1310700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1008700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>930800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>645400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>533800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>407600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>200800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>206800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>264800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>203100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>97500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>39500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>23500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>10800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>25800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>27100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>25300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>295900</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3">
         <v>301200</v>
       </c>
-      <c r="F12" s="3">
-        <v>302000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>298500</v>
-      </c>
-      <c r="H12" s="3">
-        <v>304400</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="3">
         <v>279800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>280500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>283300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>320500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>244200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>421000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>370900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>340400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>286600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>231400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>172600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>141100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>109500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>104300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>75300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>63900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>48800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>43600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>35100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>28500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>26600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>17300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>12900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>10700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>6100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>5800</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,50 +1417,53 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3">
         <v>52500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="3">
-        <v>84100</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" s="3">
         <v>41700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" s="3">
         <v>145600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-22000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>177300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1459,8 +1479,8 @@
       <c r="U14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1510,40 +1530,43 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>88900</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>96200</v>
       </c>
-      <c r="F15" s="3">
-        <v>110200</v>
-      </c>
       <c r="G15" s="3">
-        <v>102300</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>102300</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>101500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>107100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>120200</v>
       </c>
       <c r="L15" s="3">
         <v>120200</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>120200</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1557,8 +1580,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>11</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>11</v>
@@ -1575,15 +1598,15 @@
       <c r="W15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y15" s="3">
         <v>11000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>10100</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1608,20 +1631,23 @@
       <c r="AH15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>2000</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AL15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AM15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>4384700</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3">
         <v>4644700</v>
       </c>
-      <c r="F17" s="3">
-        <v>4125800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3724000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3663200</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="3">
         <v>3673100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3437900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2811800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2798000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2909000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3651600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3779300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3397600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3664200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3147400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2614600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2112100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1923900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1517600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1254800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>982600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1007300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>797600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>670700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>591100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>608200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>451100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>403300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>353100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>315700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>254800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>184000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>162000</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL17" s="3">
+      <c r="AL17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM17" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>456400</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="3">
         <v>305800</v>
       </c>
-      <c r="F18" s="3">
-        <v>202400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>82900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>71100</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J18" s="3">
         <v>-56500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-127700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>283800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>243100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>542600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-495600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-836700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-498000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-442100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-458500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-334100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-348500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-357300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-305400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-372800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-267700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-230100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-187500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-234500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-239200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-325000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-246200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-219500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-198100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-191100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-160700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-82500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-68100</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL18" s="3">
+      <c r="AL18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM18" s="3">
         <v>-52900</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,558 +1950,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-900</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="3">
         <v>11200</v>
       </c>
-      <c r="F20" s="3">
-        <v>-43500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-57600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>8600</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J20" s="3">
         <v>17300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-45400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-109400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-153900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-21400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-18700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>24200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-89600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-28900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>51000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>35900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>20600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-19100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-432700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>62900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>40800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-27800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-53200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>34300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-200</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL20" s="3">
+      <c r="AL20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>546200</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>390700</v>
       </c>
-      <c r="F21" s="3">
-        <v>356100</v>
-      </c>
       <c r="G21" s="3">
-        <v>242800</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>164800</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>27700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>513400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>356600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>384000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-476300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-844500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-402800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-258200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-420100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-331200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-287800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="X21" s="3">
         <v>-318400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-193600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-193500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-108900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-250100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-646400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-287600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-171100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-244000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-193200</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>-73900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-59400</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AL21" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>9100</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="3">
         <v>9300</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="3">
-        <v>9700</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J22" s="3">
         <v>10100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M22" s="3">
         <v>10400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>52300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>37000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>22700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>26900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>34900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>45400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>43300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>24600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10100</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>9900</v>
       </c>
       <c r="AD22" s="3">
         <v>9900</v>
       </c>
       <c r="AE22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AF22" s="3">
         <v>3000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>2300</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
-      </c>
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>547100</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="3">
         <v>326800</v>
       </c>
-      <c r="F23" s="3">
-        <v>245900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>140500</v>
-      </c>
-      <c r="H23" s="3">
-        <v>55800</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="3">
         <v>-34700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-82300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>393200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>149200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>377800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-504800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-869500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-504100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-513100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-471400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-359100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-371700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-481800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-379800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-365200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-256500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-245200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-177700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-263700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-682000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-272000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-215300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-250300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-216300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-253400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-134900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-89700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-70500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-68000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-56800</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>136300</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="3">
         <v>89200</v>
       </c>
-      <c r="F24" s="3">
-        <v>92600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>60600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>78800</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J24" s="3">
         <v>76900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>61700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>62200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>61900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-43500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>65300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>64800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>81800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>105600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>101000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>75200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>51000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>44200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>46400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>27800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>23200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>36000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>27400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>15300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>8700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>410800</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="3">
         <v>237600</v>
       </c>
-      <c r="F26" s="3">
-        <v>153300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>79900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-23000</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" s="3">
         <v>-111600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-144000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>331000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>87300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>421300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-570100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-934200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-585900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-618700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-572400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-434300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-422700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-526000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-426200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-393000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-279700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-281200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-205000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-279000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-689200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-275000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-217300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-250100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-215600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-262200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-132800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-91900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-72400</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL26" s="3">
+      <c r="AL26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM26" s="3">
         <v>-60300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>403100</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="3">
         <v>237300</v>
       </c>
-      <c r="F27" s="3">
-        <v>153300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>79900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J27" s="3">
         <v>-109700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-144000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>331000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>88100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>426800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-565300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-933100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-579800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-617600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-573000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-433400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-422700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-523600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-420000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-393000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-281500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-283800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-207600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-281100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-690400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-276600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-218300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-250700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-215600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-262700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-132700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-92100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-73100</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL27" s="3">
+      <c r="AL27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM27" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>900</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="3">
         <v>-11200</v>
       </c>
-      <c r="F32" s="3">
-        <v>43500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>57600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32" s="3">
         <v>-17300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>45400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>109400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>153900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>21400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>18700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-24200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>89600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>28900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-51000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-35900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-20600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>19100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>432700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-62900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>27800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>9600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>53200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-34300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>200</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL32" s="3">
+      <c r="AL32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>403100</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="3">
         <v>237300</v>
       </c>
-      <c r="F33" s="3">
-        <v>153300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>79900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J33" s="3">
         <v>-109700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-144000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>331000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>88100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>426800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-565300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-933100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-579800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-617600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-573000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-433400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-422700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-523600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-420000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-393000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-281500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-283800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-207600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-281100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-690400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-276600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-218300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-250700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-215600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-262700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-132700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-92100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-73100</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL33" s="3">
+      <c r="AL33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM33" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>403100</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="3">
         <v>237300</v>
       </c>
-      <c r="F35" s="3">
-        <v>153300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>79900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" s="3">
         <v>-109700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-144000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>331000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>88100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>426800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-565300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-933100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-579800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-617600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-573000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-433400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-422700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-523600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-420000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-393000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-281500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-283800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-207600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-281100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-690400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-276600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-218300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-250700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-215600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-262700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-132700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-92100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-73100</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL35" s="3">
+      <c r="AL35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM35" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,202 +3958,206 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>2183000</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="3">
         <v>2405200</v>
       </c>
-      <c r="F41" s="3">
-        <v>2538700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>2646500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>2460800</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J41" s="3">
         <v>2811100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3219900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3524400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6082700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6029900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6253400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6493200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7683700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9247800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11126200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4645400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5752600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6166900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3509000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3432800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2599700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3119000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2297200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2308100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2362500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1002800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1209200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1477100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1172400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1347400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>581500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>651100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>456800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>170100</v>
       </c>
-      <c r="AL41" s="3" t="s">
+      <c r="AM41" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6243200</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>6215400</v>
       </c>
-      <c r="F42" s="3">
-        <v>5374500</v>
-      </c>
       <c r="G42" s="3">
-        <v>3387500</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>2941000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>2547600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2762700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2174900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>506400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>864300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1042300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1287500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1116900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>911300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>706000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>962100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>309700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>126100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>42300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>14700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>30500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>102300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>9400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>8900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>700</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
-      </c>
       <c r="AE42" s="3">
         <v>0</v>
       </c>
@@ -4075,795 +4165,819 @@
         <v>0</v>
       </c>
       <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
         <v>18000</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AI42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AJ42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AK42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL42" s="3" t="s">
+      <c r="AK42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>5507100</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="3">
         <v>6057900</v>
       </c>
-      <c r="F43" s="3">
-        <v>4227800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>3464200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>3280500</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J43" s="3">
         <v>4538700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2313000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2198800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2246600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2336000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2386500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2295000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2124600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1905400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1433700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1159100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>795400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>668400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>295900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>254600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>163600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>191800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>140500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>152700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>151500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>103000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>66500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>61000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>73100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>64100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>59200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>47900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>43200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>37800</v>
       </c>
-      <c r="AL43" s="3" t="s">
+      <c r="AM43" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>172700</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="3">
         <v>143200</v>
       </c>
-      <c r="F44" s="3">
-        <v>200700</v>
-      </c>
-      <c r="G44" s="3">
-        <v>157500</v>
-      </c>
-      <c r="H44" s="3">
-        <v>142300</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J44" s="3">
         <v>125400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>116300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>98500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>107300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>109700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>122400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>127200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>139700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>117500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>128700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>99500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>92700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>64200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>61700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>61200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>34200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>26900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>21400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>22500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>25900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>37700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>19600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>16900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>13400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>9800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>7300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3900</v>
       </c>
-      <c r="AL44" s="3" t="s">
+      <c r="AM44" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="3">
         <v>263200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J45" s="3">
         <v>228800</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N45" s="3">
         <v>3348200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2773300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2769200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2765100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2953500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2609100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2530900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2075600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1913400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1654200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1487700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1222600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>970100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>849300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>757500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>652000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>566500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>513100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>424200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>383400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>281500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>218800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>163600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>122800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>98100</v>
       </c>
-      <c r="AL45" s="3" t="s">
+      <c r="AM45" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>17779300</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="3">
         <v>16857700</v>
       </c>
-      <c r="F46" s="3">
-        <v>15554200</v>
-      </c>
-      <c r="G46" s="3">
-        <v>12880700</v>
-      </c>
-      <c r="H46" s="3">
-        <v>12381300</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J46" s="3">
         <v>11773900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11973900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11475800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12440300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12688000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12577900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12972100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13829900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15135400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16003700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9397100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9025900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8939000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5563100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5251000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4050600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4410100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3317800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3249700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3192500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1710700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1808500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1979300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1642300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1720700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>866800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>868200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>628600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>309900</v>
       </c>
-      <c r="AL46" s="3" t="s">
+      <c r="AM46" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>2828500</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="3">
         <v>2694300</v>
       </c>
-      <c r="F47" s="3">
-        <v>2974600</v>
-      </c>
-      <c r="G47" s="3">
-        <v>3769500</v>
-      </c>
-      <c r="H47" s="3">
-        <v>4024600</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J47" s="3">
         <v>4262600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3162700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3183300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1789200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1275300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1372000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1383900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1455900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1081800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>370600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>331900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>353500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>307600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>219100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>195200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>143200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>113800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>99100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>100400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>107100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>111000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>118200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>71000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>58500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>28200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>27100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>45100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>45400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>45100</v>
       </c>
-      <c r="AL47" s="3" t="s">
+      <c r="AM47" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>2248300</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="3">
         <v>2152500</v>
       </c>
-      <c r="F48" s="3">
-        <v>2327700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2188700</v>
-      </c>
-      <c r="H48" s="3">
-        <v>2058500</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J48" s="3">
         <v>2223700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2243800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2308400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2372400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2345700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2457200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2214700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2101500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1679600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1353300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>830200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>628600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>621000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>573400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>523500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>486900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>501600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>463100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>425900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>406300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>192400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>147400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>121900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>93900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>74300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>47900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>34100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>32400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>31100</v>
       </c>
-      <c r="AL48" s="3" t="s">
+      <c r="AM48" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>126600</v>
-      </c>
-      <c r="E49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="3">
         <v>134900</v>
       </c>
-      <c r="F49" s="3">
-        <v>144600</v>
-      </c>
-      <c r="G49" s="3">
-        <v>142100</v>
-      </c>
-      <c r="H49" s="3">
-        <v>152900</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J49" s="3">
         <v>163600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>173400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>176300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>182300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>295200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>482100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>462300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>624000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>592100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>525400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>518500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>509300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>256100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>244000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>260500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>263300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>46000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>45900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>43800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>44900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>43800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>56600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>60500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>64600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>68300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>73000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>24300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>27200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>30000</v>
       </c>
-      <c r="AL49" s="3" t="s">
+      <c r="AM49" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>194800</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="3">
         <v>139600</v>
       </c>
-      <c r="F52" s="3">
-        <v>146000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>136000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>127200</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J52" s="3">
         <v>97900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>140400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>164600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>160600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>398600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>393200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>434700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>323400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>267000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>295700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>445400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>405300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>332000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>360900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>374100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>288900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>152700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>156000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>199200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>176100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>134700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>121800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>122600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>111100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>96700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>106400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>92500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>78900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>69700</v>
       </c>
-      <c r="AL52" s="3" t="s">
+      <c r="AM52" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>23843100</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="3">
         <v>22625500</v>
       </c>
-      <c r="F54" s="3">
-        <v>21691700</v>
-      </c>
-      <c r="G54" s="3">
-        <v>19570000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>19095000</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J54" s="3">
         <v>18883200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18025100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17652300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17243900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17002800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17282300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17467700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18334600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18756000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>18548700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11523000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10922600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10455700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6960600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6604300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5232800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5224200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4081900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4019100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3927000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2192700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2252400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2355400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1970500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1988300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1121200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1064200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>812400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>485800</v>
       </c>
-      <c r="AL54" s="3" t="s">
+      <c r="AM54" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,174 +5622,178 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>320900</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="3">
         <v>604700</v>
       </c>
-      <c r="F57" s="3">
-        <v>274800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>293700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>280000</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J57" s="3">
         <v>406000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>267900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>219000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>212300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>258600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>289800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>239000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>287100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>213600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>232700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>179600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>152900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>121600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>118400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>96700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>51000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>69400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>48100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>32400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>38100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>37200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>25200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>33900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6000</v>
       </c>
-      <c r="AL57" s="3" t="s">
+      <c r="AM57" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>1580600</v>
-      </c>
-      <c r="E58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="3">
         <v>1583400</v>
       </c>
-      <c r="F58" s="3">
-        <v>610300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>518400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>529700</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J58" s="3">
         <v>592900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>380200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>382800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>406100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1436000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>80200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>100000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>11</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -5668,34 +5802,34 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>2400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>30700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>24000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>25800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>900</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>2000</v>
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AH58" s="3">
         <v>2000</v>
@@ -5707,453 +5841,468 @@
         <v>2000</v>
       </c>
       <c r="AK58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AL58" s="3">
         <v>1900</v>
       </c>
-      <c r="AL58" s="3" t="s">
+      <c r="AM58" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>7735900</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="3">
         <v>7179300</v>
       </c>
-      <c r="F59" s="3">
-        <v>6556000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>6000900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>5861600</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J59" s="3">
         <v>5536800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4785700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4564500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4760800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5241000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6681300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6500800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6567000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6862900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6188300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5704000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4924700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4514400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3654100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2890200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2375300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2262300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1979600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1663600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1371000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1148500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>921400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>744000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>738400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>627000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>438500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>323700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>276700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>255900</v>
       </c>
-      <c r="AL59" s="3" t="s">
+      <c r="AM59" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>11801300</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="3">
         <v>11296200</v>
       </c>
-      <c r="F60" s="3">
-        <v>9589400</v>
-      </c>
-      <c r="G60" s="3">
-        <v>8617200</v>
-      </c>
-      <c r="H60" s="3">
-        <v>8487200</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J60" s="3">
         <v>8168900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7030800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6575700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6660200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6935700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7051400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6739800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6854100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7176400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6421000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5883600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5077600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4636100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3772500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2986900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2428600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2362400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2051700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1721800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1410100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1186500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>946500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>777900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>752300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>637700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>449800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>333800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>288100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>263800</v>
       </c>
-      <c r="AL60" s="3" t="s">
+      <c r="AM60" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2567500</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>2540800</v>
       </c>
-      <c r="F61" s="3">
-        <v>3793400</v>
-      </c>
       <c r="G61" s="3">
-        <v>3724200</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>3629300</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>3869500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4234400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4178700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4111800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3338800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4148000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4177300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4175400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3475700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3503500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1282500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1757600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1840400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1920900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2109200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1374800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1356700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>446600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>439600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>582700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1062800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1116400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1145800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>745700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>727000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>674400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>624800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>355000</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>209600</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="3">
         <v>200700</v>
       </c>
-      <c r="F62" s="3">
-        <v>182000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>143800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>87400</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J62" s="3">
         <v>74500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>80300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>82600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>85100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>917500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1126800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1115800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1013800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>679500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>813800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>758000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>647000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>559000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>494400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>615700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>462400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>332500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>324100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>418800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>400200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>182800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>161300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>200200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>177900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>148500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>208100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>179600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>157100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>142600</v>
       </c>
-      <c r="AL62" s="3" t="s">
+      <c r="AM62" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>14768700</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="3">
         <v>14147900</v>
       </c>
-      <c r="F66" s="3">
-        <v>13663100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>12603700</v>
-      </c>
-      <c r="H66" s="3">
-        <v>12326100</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J66" s="3">
         <v>12185600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11447100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11032100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11052300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11287100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12385100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12094500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12073400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11357300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10761500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7962900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7518900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7072800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6219300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5750500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4312200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4061700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2829400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2585700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2397500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2435800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2227300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2126800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1681400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1519300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1340700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1138200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>800200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>406400</v>
       </c>
-      <c r="AL66" s="3" t="s">
+      <c r="AM66" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6948,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="AH70" s="3">
-        <v>205100</v>
+        <v>0</v>
       </c>
       <c r="AI70" s="3">
         <v>205100</v>
@@ -6960,10 +7128,13 @@
         <v>205100</v>
       </c>
       <c r="AL70" s="3">
+        <v>205100</v>
+      </c>
+      <c r="AM70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-7735000</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="3">
         <v>-8138000</v>
       </c>
-      <c r="F72" s="3">
-        <v>-8375300</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-8524100</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-8606000</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J72" s="3">
         <v>-8582300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8472600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8323400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8645000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8733100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-9159800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8594600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7661400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7195400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6577700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6004700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5571300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5148600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4625000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4205000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3812100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3530500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3246800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3039200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2758100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2067700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1791100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1572800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1322100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1106500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-843800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-670100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-578000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-505000</v>
       </c>
-      <c r="AL72" s="3" t="s">
+      <c r="AM72" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>8963400</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="3">
         <v>8372300</v>
       </c>
-      <c r="F76" s="3">
-        <v>7916400</v>
-      </c>
-      <c r="G76" s="3">
-        <v>6867300</v>
-      </c>
-      <c r="H76" s="3">
-        <v>6667100</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J76" s="3">
         <v>6593800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6467300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6511500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6093300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5715700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4897200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5373200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6261200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7398700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7787300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3560200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3403700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3382900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>741200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>853800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>920600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1162400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1252500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1433400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1529500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-243100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>25100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>228600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>289100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>469000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-424600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-279000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-192800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-125700</v>
       </c>
-      <c r="AL76" s="3" t="s">
+      <c r="AM76" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>403100</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="3">
         <v>237300</v>
       </c>
-      <c r="F81" s="3">
-        <v>153300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>79900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J81" s="3">
         <v>-109700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-144000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>331000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>88100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>426800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-565300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-933100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-579800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-617600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-573000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-433400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-422700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-523600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-420000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-393000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-281500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-283800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-207600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-281100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-690400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-276600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-218300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-250700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-215600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-262700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-132700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-92100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-73100</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL81" s="3">
+      <c r="AL81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM81" s="3">
         <v>-64900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,41 +8195,42 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>102300</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="3">
         <v>412200</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G83" s="3">
-        <v>-120200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>120200</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J83" s="3">
         <v>404900</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L83" s="3">
         <v>-89700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>89700</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -8056,21 +8255,21 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>11</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y83" s="3">
         <v>38200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>34600</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>11</v>
       </c>
@@ -8083,32 +8282,35 @@
       <c r="AD83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
+      <c r="AE83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>11</v>
+      <c r="AG83" s="3">
+        <v>0</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>8800</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AL83" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AM83" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>756900</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="3">
         <v>1021000</v>
       </c>
-      <c r="F89" s="3">
-        <v>1170100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>617900</v>
-      </c>
-      <c r="H89" s="3">
-        <v>468500</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J89" s="3">
         <v>278800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>599800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>595500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>605500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>319700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-166300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-485500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-723700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-304800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>62700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>132400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>318300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>185400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>296000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>298100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-223700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-27800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>380800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-265300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-324400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>112300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-188800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-94400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-38200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-89800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-65400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-65800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-42100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-36500</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,41 +9027,42 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="3">
         <v>-317900</v>
       </c>
-      <c r="F91" s="3">
-        <v>90800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-64000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-27000</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J91" s="3">
         <v>-64600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-44000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-101000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -8866,21 +9087,21 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>11</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-50100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-42400</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>11</v>
       </c>
@@ -8893,32 +9114,35 @@
       <c r="AD91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>11</v>
+      <c r="AG91" s="3">
+        <v>0</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AL91" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AM91" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-1114700</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1761100</v>
       </c>
-      <c r="F94" s="3">
-        <v>-1716100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-709900</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-853800</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1048600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-888300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3193900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-673800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>51500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-402100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-947500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1130700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1775500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-341900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1145500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-504300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-667400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>91300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-163700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-147100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-143700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-157700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>29400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-91300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-157100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-51100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-50100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>12900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-13400</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>274400</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="3">
         <v>700200</v>
       </c>
-      <c r="F100" s="3">
-        <v>557800</v>
-      </c>
-      <c r="G100" s="3">
-        <v>242600</v>
-      </c>
-      <c r="H100" s="3">
-        <v>183800</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J100" s="3">
         <v>183400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>124500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>59200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-513700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>474000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>297600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>142400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>386000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6835200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>138800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>41600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2198600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>747700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>811600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-24800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1045000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>989800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-983100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1527900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-149800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>151700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>545300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>927400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>69500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>270000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>357000</v>
       </c>
-      <c r="AK100" s="3">
-        <v>0</v>
-      </c>
       <c r="AL100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-72800</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="3">
         <v>68300</v>
       </c>
-      <c r="F101" s="3">
-        <v>-54200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-71600</v>
-      </c>
-      <c r="H101" s="3">
-        <v>49500</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J101" s="3">
         <v>109100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-124900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-119700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>109100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-124900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-119700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-33000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>14500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-46300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>59000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>13000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>60500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-51800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>23200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>12900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>15300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-17300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>6200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-65600</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-184700</v>
       </c>
-      <c r="F102" s="3">
-        <v>191100</v>
-      </c>
       <c r="G102" s="3">
-        <v>105700</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>-274300</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-518000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-218100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2671100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-33400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-219200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1255100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1687800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6523100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-859700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-190800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2068300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>855400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1006400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-447300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>896700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1225800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1231900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1420700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-648000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>273600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>299300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-110600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>842800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-69600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>194300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>286700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-31900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-18000</v>
       </c>
     </row>
